--- a/workspaces/btc_daily_14days/stoch/stoch_d_14.xlsx
+++ b/workspaces/btc_daily_14days/stoch/stoch_d_14.xlsx
@@ -575,46 +575,46 @@
         <v>106</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.883920170356063</v>
+        <v>7.858603436037242</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10.99202056355811</v>
+        <v>10.95701320038336</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.43125248246756</v>
+        <v>13.38832115018158</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.73270108597541</v>
+        <v>10.69808221381948</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.1407354411412</v>
+        <v>11.10482841960091</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.607520751304612</v>
+        <v>8.580011799671361</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.24883066295518</v>
+        <v>13.20627112675701</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.003990609140608</v>
+        <v>8.97507282694928</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.273283961237304</v>
+        <v>3.263141182069027</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.476439030416564</v>
+        <v>1.472223865812815</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.271298346440119</v>
+        <v>1.268008265853489</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.306100375051408</v>
+        <v>1.302614363021192</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.007527093997162</v>
+        <v>-1.003593832644391</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1889699190840588</v>
+        <v>0.1892211674810582</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>128</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.756561679789669</v>
+        <v>3.743617040998046</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.543164069995576</v>
+        <v>-2.5346862913213</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.157206324772162</v>
+        <v>-2.150214372262923</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.881963642381955</v>
+        <v>1.875068661019917</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.125572727049629</v>
+        <v>2.117865516872897</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.206115047830195</v>
+        <v>3.195138283719558</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.904711696504982</v>
+        <v>3.891056933528127</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.089631745965526</v>
+        <v>1.085628402392437</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.811314944774345</v>
+        <v>1.805483256038166</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.308720590455906</v>
+        <v>3.298075667221113</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.8123688618684213</v>
+        <v>-0.8088373263716733</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.7888847780430837</v>
+        <v>0.7869301490990495</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4162856570520077</v>
+        <v>-0.4141060907553182</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.969550599787596</v>
+        <v>2.960447582575043</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.211259666367049</v>
+        <v>3.223241064115875</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.956711985869873</v>
+        <v>4.97386125233222</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.205474580938208</v>
+        <v>1.209739941639512</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.679707590188407</v>
+        <v>2.689897679974862</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.813362391979709</v>
+        <v>2.824039221867203</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.095783454897308</v>
+        <v>1.100176451796457</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.683678354919287</v>
+        <v>1.690557461407508</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.215869912165616</v>
+        <v>1.220607303180358</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.499939072238789</v>
+        <v>2.508606373771769</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3028159812447413</v>
+        <v>0.3037188322865845</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.442879537265767</v>
+        <v>1.446982466174482</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.477922623382355</v>
+        <v>1.482431258489655</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2901890168448418</v>
+        <v>-0.2920864297752743</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.014952569447424</v>
+        <v>1.017880015008146</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.153302265788049</v>
+        <v>-2.160046622566782</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.765893644897091</v>
+        <v>-3.779452241820493</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.686459190790899</v>
+        <v>4.704219712993456</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.775861568700662</v>
+        <v>2.787549033766503</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.918762621673999</v>
+        <v>2.931025754115524</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.913721800119717</v>
+        <v>-2.923833902302619</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.043363720852739</v>
+        <v>-5.060875747362196</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.786670067484444</v>
+        <v>-2.796373272567699</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.803388143516905</v>
+        <v>-0.8061075869714927</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.071829263477774</v>
+        <v>1.075709038764295</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.8662597451544585</v>
+        <v>0.8686642159660849</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.828322144137985</v>
+        <v>-1.835675495023985</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.179386820109862</v>
+        <v>-1.184821694906837</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.613455898780579</v>
+        <v>-1.620031869479398</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>143</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.542389369161022</v>
+        <v>-3.531879024600919</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.938095302793343</v>
+        <v>3.925454168689775</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.452798260403874</v>
+        <v>-3.442520577690452</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-11.02223611118581</v>
+        <v>-10.98831225541132</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-6.663516684943311</v>
+        <v>-6.643672095189714</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.166078175513483</v>
+        <v>-2.159425730712279</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.652504790677632</v>
+        <v>-3.641293337977032</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.421102084508483</v>
+        <v>-3.410369333929658</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.483314286068705</v>
+        <v>-3.472256195667676</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.037937545398528</v>
+        <v>-5.021755784484974</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.9467207785884</v>
+        <v>-5.926955063237507</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.107869414832038</v>
+        <v>-3.097165991902841</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.7236197130927309</v>
+        <v>-0.7202178056447863</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.875832402876419</v>
+        <v>-1.869097871969892</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.875117709522954</v>
+        <v>-2.887779468586544</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.778782089122402</v>
+        <v>-6.809432427877283</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.592985084540643</v>
+        <v>-2.60440720784608</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1712766716708529</v>
+        <v>-0.1718976974863793</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.8184266726715705</v>
+        <v>0.8233129230760454</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.706307179171262</v>
+        <v>-2.718775703672904</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.791998237117241</v>
+        <v>-2.804816391960287</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.20123598663465</v>
+        <v>-0.202418759187303</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5026528349168089</v>
+        <v>0.5045277164096973</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.115423025343766</v>
+        <v>-1.12151951657038</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.619033464746984</v>
+        <v>-3.637880600138217</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.150858211935969</v>
+        <v>-3.167096061832908</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.025039640666556</v>
+        <v>1.028033942606797</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.555163340819377</v>
+        <v>-2.568398571270933</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>113</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.820871948528563</v>
+        <v>-3.808931988598061</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.893253043891875</v>
+        <v>-1.886948131405866</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.288916493819755</v>
+        <v>-2.281790320920813</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.045041103858892</v>
+        <v>-3.035550353811516</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.584779166069083</v>
+        <v>-3.574368985688537</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.061205385239916</v>
+        <v>-5.044963936012138</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-5.14771325900422</v>
+        <v>-5.131221790494024</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-7.391351469266972</v>
+        <v>-7.36786834332085</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.793328576068077</v>
+        <v>-4.777975244294673</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.985488056740401</v>
+        <v>-2.975283370407176</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.417550686411467</v>
+        <v>-1.411145658933279</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.270437416256257</v>
+        <v>-2.26171825380024</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.354814970769596</v>
+        <v>-5.336840121382103</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.2219956076444731</v>
+        <v>0.2226157241683211</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4273226177306313</v>
+        <v>-0.430176765723715</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4405279841870424</v>
+        <v>0.4419259491569605</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.04556827314807776</v>
+        <v>0.04552215676081772</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.312220233742742</v>
+        <v>4.334936673518072</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.190387511675262</v>
+        <v>-1.195902013589887</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.073291196141298</v>
+        <v>4.093635595202564</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6773514245311176</v>
+        <v>0.6795104679451001</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.447589778495512</v>
+        <v>-1.457120361573537</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6805194478737064</v>
+        <v>-0.685534714451272</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.610640596862822</v>
+        <v>2.622655513371008</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.19208803604166</v>
+        <v>6.221597703898581</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5.396908188780998</v>
+        <v>5.422647527910684</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.636453612296023</v>
+        <v>6.669059583632439</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.226374910112384</v>
+        <v>5.252114249242069</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>123</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-6.151974905575827</v>
+        <v>-6.132697366246077</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.326399212360805</v>
+        <v>-5.309523455779726</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.65551904150788</v>
+        <v>-1.65026818491036</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.22245392821727</v>
+        <v>-7.200560030909081</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-6.949888358092835</v>
+        <v>-6.92891990912117</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-9.097891082142297</v>
+        <v>-9.069559834227256</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-13.25959900325083</v>
+        <v>-13.21808929984361</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-12.91790858558537</v>
+        <v>-12.87701329370617</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-16.24426810276677</v>
+        <v>-16.19349172286415</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-13.84058839556025</v>
+        <v>-13.79722620755619</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-8.337969712058644</v>
+        <v>-8.310922621304854</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.856746312648887</v>
+        <v>-5.837515073715515</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-9.540061492415568</v>
+        <v>-9.509802204985633</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-10.10484090081146</v>
+        <v>-10.07308900279045</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.942713682528648</v>
+        <v>-3.961836492212925</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.4821394052595736</v>
+        <v>-0.486033695359481</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.327724844036837</v>
+        <v>-2.33855692958339</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.19829789345777</v>
+        <v>-2.208914469823497</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.012617256577911</v>
+        <v>-2.022231177047765</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.89386331931054</v>
+        <v>-3.913328035718287</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.707227191827428</v>
+        <v>-4.731651303104258</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.177905184558476</v>
+        <v>-5.204994849470275</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.514641182794833</v>
+        <v>-4.538920676762594</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-8.586635250312902</v>
+        <v>-8.628393497331118</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-7.33719812794741</v>
+        <v>-7.373292807050156</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-8.030436590690151</v>
+        <v>-8.068836657003999</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-7.72186638898345</v>
+        <v>-7.75916426064979</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.746779422675701</v>
+        <v>-6.779515921074236</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>112</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.600581177353035</v>
+        <v>-1.594004016168029</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3592422792876064</v>
+        <v>0.3594942938770131</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8577174174413642</v>
+        <v>0.8558966171652571</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.775971439249567</v>
+        <v>2.768659963100028</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.131931003601707</v>
+        <v>3.123400123355879</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.535610829727275</v>
+        <v>2.530234075503614</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.029979659571374</v>
+        <v>6.015267063467824</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10.03896268343103</v>
+        <v>10.01277393436444</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.29448998350184</v>
+        <v>7.276476213244088</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>7.337100084037928</v>
+        <v>7.319208171073299</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.132024365622243</v>
+        <v>7.114454846755933</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>8.958003581968129</v>
+        <v>8.934552289815443</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.745293194426061</v>
+        <v>6.728583393156249</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.4139717026912</v>
+        <v>3.406876154003768</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>120</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.006561679790024755</v>
+        <v>0.008714303114061295</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.063457244375577</v>
+        <v>5.049037157311005</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.338229107921585</v>
+        <v>6.3191234504853</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.636713798737212</v>
+        <v>5.619803649669386</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.934313468623699</v>
+        <v>5.916255753571988</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>12.91331915778056</v>
+        <v>12.87503765009967</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8.65617963769381</v>
+        <v>8.631930562823698</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>7.355131394272398</v>
+        <v>7.334953914448477</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.78829303665507</v>
+        <v>4.776476213244088</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.263347811267678</v>
+        <v>2.259684361549311</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.402021356946712</v>
+        <v>5.388264370565061</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.25750192556707</v>
+        <v>1.255980861244005</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.0004557815349954808</v>
+        <v>0.002392916965774816</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.257864987789851</v>
+        <v>-2.247885750757753</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-8.945051223435968</v>
+        <v>-9.079419381618827</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-13.34423824365818</v>
+        <v>-13.53281135672135</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-10.51678795169722</v>
+        <v>-10.66198032344722</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-12.81286527587319</v>
+        <v>-12.99042837405026</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-11.73855823483093</v>
+        <v>-11.89998987336799</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-12.25428750506805</v>
+        <v>-12.42568230227697</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-9.108461542836551</v>
+        <v>-9.242345725734985</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-13.61883962825289</v>
+        <v>-13.81625896097381</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-13.22503140669426</v>
+        <v>-13.42024509823132</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-14.86910902539123</v>
+        <v>-15.09004241440698</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-18.30816713091513</v>
+        <v>-18.57348426331453</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-18.27485727717609</v>
+        <v>-18.5391011059691</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-13.83587326516658</v>
+        <v>-14.04132293002876</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-13.58776188829961</v>
+        <v>-13.79160159775248</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8963921882647909</v>
+        <v>0.8943290870849836</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.410096678936746</v>
+        <v>-2.431328228240936</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.339142001825728</v>
+        <v>-2.357025857178257</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.333551747541982</v>
+        <v>0.3317256895645784</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.038941787950911</v>
+        <v>4.061659058500233</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9432741075538971</v>
+        <v>0.9447476409686573</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.534391438600132</v>
+        <v>-2.557042486685901</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.148988487327337</v>
+        <v>-2.171070909120822</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.153186515392683</v>
+        <v>-8.214976778208907</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-7.297440863179567</v>
+        <v>-7.355700253834925</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.802835204651629</v>
+        <v>-5.851051868750993</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-6.618261775816919</v>
+        <v>-6.671369566106414</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.638756524367082</v>
+        <v>-3.672820758247894</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.691239054300084</v>
+        <v>-1.713697716569897</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.274824097726992</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.9304087585710548</v>
+        <v>-0.9428647035733775</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.5316266715168538</v>
+        <v>-0.5386612123205197</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.726736125703987</v>
+        <v>-4.759770117169801</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.296069275462997</v>
+        <v>-1.305857996120054</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.384548068628014</v>
+        <v>1.38876417013919</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.464450323300085</v>
+        <v>-3.493196059648859</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.519320379836429</v>
+        <v>-5.562523900573609</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.396211167506081</v>
+        <v>-2.423523786755908</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.829657892379615</v>
+        <v>-4.873648971783837</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-8.21455076547791</v>
+        <v>-8.278402296101419</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-11.36083643021031</v>
+        <v>-11.44401913875598</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-10.18930112854807</v>
+        <v>-10.26427374970088</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-9.145801933158637</v>
+        <v>-9.214552417424784</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2538144270427765</v>
+        <v>0.2448858182332856</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.65446248262478</v>
+        <v>-4.711134683303975</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-8.346034485924413</v>
+        <v>-8.433256771873616</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.017979155515221</v>
+        <v>-6.085275577094549</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-8.146598493631842</v>
+        <v>-8.229071916459219</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.654583131675849</v>
+        <v>-5.715642049265902</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-7.933249363967128</v>
+        <v>-8.024151112794364</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.994468396641359</v>
+        <v>-4.051412789462745</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.7496788103744905</v>
+        <v>-0.7790793423117179</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.587555798926786</v>
+        <v>-1.629204527339397</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.511293171262928</v>
+        <v>1.499375481676353</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4465169298518248</v>
+        <v>0.4226475279106765</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.273403055304328</v>
+        <v>-3.330940416367554</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.026306336558406</v>
+        <v>-3.081219084091018</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>117</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.920788747560209</v>
+        <v>-2.914534688982357</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.96825979642248</v>
+        <v>-1.963076861368073</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.36312850301907</v>
+        <v>-2.357945567964663</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.378174515710533</v>
+        <v>-1.374211420125249</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.480698294885066</v>
+        <v>-4.472788081461118</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.475572503838976</v>
+        <v>-2.470418935625915</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.707498176582085</v>
+        <v>-1.702082177217733</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.889601208196432</v>
+        <v>-3.880472618522134</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.040855969017478</v>
+        <v>2.041433478201547</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.235266537904678</v>
+        <v>-2.227495125629794</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7281749869662519</v>
+        <v>-0.7228467405456698</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.017908822423649</v>
+        <v>1.020938126201088</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.394812414396846</v>
+        <v>-5.382222467649413</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.576674764785324</v>
+        <v>-2.568398571270556</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.345290172062036</v>
+        <v>-4.39331180183607</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-5.956863785025874</v>
+        <v>-6.019884458547359</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.833452693562727</v>
+        <v>3.854666618862126</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.591849729385331</v>
+        <v>-1.616581948897348</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.573432759245982</v>
+        <v>1.577664742525464</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9079917077018891</v>
+        <v>-0.9248908596433694</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.493474051540971</v>
+        <v>5.521644053846735</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.9253192806499868</v>
+        <v>0.9122424545665737</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.645060135208524</v>
+        <v>3.654980886141502</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>7.442745990282049</v>
+        <v>7.477752897374614</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.38416550547079</v>
+        <v>5.403840694552571</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.92284586322701</v>
+        <v>-2.972991101372813</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.264220181164362</v>
+        <v>-4.327825151570266</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.237482740953652</v>
+        <v>-1.27436550153697</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>5.571077808822167</v>
+        <v>5.60997918996658</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.110041830266631</v>
+        <v>6.151339503437136</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3388290376485301</v>
+        <v>0.3307725385949993</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.756724281356874</v>
+        <v>-2.801309478317265</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.370414313633461</v>
+        <v>-4.426077934567054</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-4.547557973276682</v>
+        <v>-4.607320047162609</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.552298671041044</v>
+        <v>-3.608383980052977</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.083388457711123</v>
+        <v>-5.162523900573611</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-9.449507540125737</v>
+        <v>-9.571349873712684</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-10.28494779761214</v>
+        <v>-10.42147505874011</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-10.48861334951899</v>
+        <v>-10.62622838305794</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-9.372375559511497</v>
+        <v>-9.504888703972881</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-7.632728108570099</v>
+        <v>-7.751230271439773</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-5.237789641948289</v>
+        <v>-5.327595895685221</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.952153916540247</v>
+        <v>-2.994289507720396</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.85829081911924</v>
+        <v>1.8579717904597</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-4.958596236101094</v>
+        <v>-5.015264296970663</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.993480718172492</v>
+        <v>-3.03783046348277</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-8.119057896547417</v>
+        <v>-8.206400324959297</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.399597610207799</v>
+        <v>-1.426957888987324</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.71487772130169</v>
+        <v>-3.769414575866293</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.252795425217826</v>
+        <v>-3.310672048721763</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.230711960486424</v>
+        <v>-4.297597860829981</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.232082083691722</v>
+        <v>-3.295871194006061</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.353237513521961</v>
+        <v>-4.426550444249571</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.313708920435246</v>
+        <v>-4.392167286904353</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.89241207959541</v>
+        <v>-2.960570045997393</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.649894357357006</v>
+        <v>-2.710848713721106</v>
       </c>
     </row>
     <row r="26">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 8.15</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4079~4092</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4079</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.1214199398095701</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 11.16</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3973~3986</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3973</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.08500881694856588</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 14.17</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3845~3858</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3845</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.2124637219725471</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 17.18</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3697~3709</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3697</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.3500034320999674</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 20.2</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3551~3562</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3551</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.2755831826468125</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 23.21</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3408~3419</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3408</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.1389487033629422</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 26.22</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3278~3288</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3278</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.02993467057493859</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 29.23</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3165~3175</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3165</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.1049868766404174</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 32.24</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3045~3054</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3045</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.1260770694429425</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 35.25</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2922~2931</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2922</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.3895367736146582</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 38.27</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2785~2793</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2785</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.6035899647882275</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 41.28</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2673~2681</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2673</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.6956702213789825</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 44.29</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2553~2561</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2553</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.7279595712386779</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 47.3</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2431~2437</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2431</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.220143953076857</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 50.31</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2314~2319</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2314</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.236617738435996</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 53.32</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2189~2193</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2189</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.177332313624952</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 56.34</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2099~2102</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2099</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.217313344870902</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 59.35</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1982~1985</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1982</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.461221629412186</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 62.36</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1875~1877</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1875</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.795320337222094</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 65.37</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1783~1784</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1783</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.598489930911107</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 68.38</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1675~1675</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1675</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.894621381282569</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 71.39</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1539~1539</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1539</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>2.282390139829012</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 74.41</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1401~1401</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1401</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>2.181793656949189</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 77.42</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1250~1250</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1250</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>2.786561679790019</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 80.43</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1103~1103</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1103</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>2.991602477614137</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 83.44</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>930~930</t>
-        </is>
+      <c r="B31" t="n">
+        <v>930</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.882905765811529</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 86.45</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>749~749</t>
-        </is>
+      <c r="B32" t="n">
+        <v>749</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>2.246214550284016</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 89.46</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>529~529</t>
-        </is>
+      <c r="B33" t="n">
+        <v>529</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>1.381797974686059</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 92.48</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>282~282</t>
-        </is>
+      <c r="B34" t="n">
+        <v>282</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>1.052660970570173</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 95.49</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-6.064866891638545</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 8.15</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-4.874390701162362</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 11.16</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>190~190</t>
-        </is>
+      <c r="B7" t="n">
+        <v>190</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2.243403785053189</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 14.17</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>318~318</t>
-        </is>
+      <c r="B8" t="n">
+        <v>318</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>2.852473629475561</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 17.18</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>466~467</t>
-        </is>
+      <c r="B9" t="n">
+        <v>466</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>2.966947118762185</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 20.2</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>612~614</t>
-        </is>
+      <c r="B10" t="n">
+        <v>612</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1.741089367086445</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 23.21</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>755~757</t>
-        </is>
+      <c r="B11" t="n">
+        <v>755</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.7430213891691508</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 26.22</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>885~888</t>
-        </is>
+      <c r="B12" t="n">
+        <v>885</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.2092643824927194</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 29.23</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>998~1001</t>
-        </is>
+      <c r="B13" t="n">
+        <v>998</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.2456860724577297</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 32.24</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1118~1122</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1118</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.2652743273400944</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 35.25</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1241~1245</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1241</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.8468519748284464</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 38.27</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1378~1383</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1378</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.15576659208272</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 41.28</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1490~1495</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1490</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-1.189090494123015</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 44.29</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1610~1615</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1610</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.100249465720808</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 47.3</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1732~1739</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1732</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.659625784269785</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 50.31</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1849~1857</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1849</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.497207840942337</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 53.32</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1974~1983</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1974</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.257936555207451</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 56.34</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2064~2074</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2064</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.191606111916826</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 59.35</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2181~2191</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2181</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.283944938192633</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 62.36</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2288~2299</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2288</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.427757589457471</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 65.37</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2380~2392</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2380</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.155645678069504</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 68.38</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2488~2501</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2488</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.233942118690578</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 71.39</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2624~2637</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2624</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.298899071063225</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 74.41</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2762~2775</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2762</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.070014896786553</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 77.42</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2913~2926</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2913</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-1.160560671542854</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 80.43</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3060~3073</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3060</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-1.045341997398388</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 83.44</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3233~3246</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3233</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.7990452210109638</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 86.45</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3414~3427</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3414</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.4654254809920033</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 89.46</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3634~3647</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3634</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.1764654658090947</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 92.48</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3881~3894</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3881</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.05378757547448743</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 95.49</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4079~4092</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4079</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.1458578674733104</v>

--- a/workspaces/btc_daily_14days/stoch/stoch_d_14.xlsx
+++ b/workspaces/btc_daily_14days/stoch/stoch_d_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Stoch D-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Stoch D-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>106</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.858603436037242</v>
+        <v>7.871090161082158</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10.95701320038336</v>
+        <v>10.96989112122573</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.38832115018158</v>
+        <v>13.40130044357</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.69808221381948</v>
+        <v>10.71103460126481</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.10482841960091</v>
+        <v>11.11791505025447</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.580011799671361</v>
+        <v>8.593032024004152</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.20627112675701</v>
+        <v>13.21931952016672</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.97507282694928</v>
+        <v>8.988236786680936</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.263141182069027</v>
+        <v>3.2763238637421</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.472223865812815</v>
+        <v>1.485615468184179</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.268008265853489</v>
+        <v>1.281455304495701</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.302614363021192</v>
+        <v>1.316059826537419</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.003593832644391</v>
+        <v>-0.9900413676993125</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1892211674810582</v>
+        <v>0.1787915317829061</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>128</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.743617040998046</v>
+        <v>3.756098403458807</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.5346862913213</v>
+        <v>-2.521820709020602</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.150214372262923</v>
+        <v>-2.137247720014493</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.875068661019917</v>
+        <v>1.88801389422968</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.117865516872897</v>
+        <v>2.130945615854408</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.195138283719558</v>
+        <v>3.208154491733893</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.891056933528127</v>
+        <v>3.904100202733176</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.085628402392437</v>
+        <v>1.098788341207914</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.805483256038166</v>
+        <v>1.818664531448363</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.298075667221113</v>
+        <v>3.311466961403397</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.8088373263716733</v>
+        <v>-0.7953913201802862</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.7869301490990495</v>
+        <v>0.8003751363420477</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4141060907553182</v>
+        <v>-0.4005538085887679</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.960447582575043</v>
+        <v>2.950017946877246</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.223241064115875</v>
+        <v>3.211737609547292</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.97386125233222</v>
+        <v>4.952404601486521</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.209739941639512</v>
+        <v>1.214168757802248</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.689897679974862</v>
+        <v>2.682444973134388</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.824039221867203</v>
+        <v>2.815747250038847</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.100176451796457</v>
+        <v>1.10439671781338</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.690557461407508</v>
+        <v>1.689829072275174</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.220607303180358</v>
+        <v>1.224283577898845</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.508606373771769</v>
+        <v>2.504438499817681</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3037188322865845</v>
+        <v>0.315301169239099</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.446982466174482</v>
+        <v>1.452215838583037</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.482431258489655</v>
+        <v>1.486851494188556</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2920864297752743</v>
+        <v>-0.2747366347334008</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.017880015008146</v>
+        <v>1.293138752246378</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>146</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.160046622566782</v>
+        <v>-2.146967716078841</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.779452241820493</v>
+        <v>-3.765466444050453</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.704219712993456</v>
+        <v>4.715947347599901</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.787549033766503</v>
+        <v>2.799709808306638</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.931025754115524</v>
+        <v>2.943279315712942</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.923833902302619</v>
+        <v>-2.909956769525415</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.060875747362196</v>
+        <v>-5.046412634838546</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.796373272567699</v>
+        <v>-2.782379280801685</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.8061075869714927</v>
+        <v>-0.7926183925957915</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.075709038764295</v>
+        <v>1.088912139358264</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.8686642159660849</v>
+        <v>0.8820358251954232</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.835675495023985</v>
+        <v>-1.821567528496345</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.184821694906837</v>
+        <v>-1.561146887580755</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.620031869479398</v>
+        <v>-1.63046150517755</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>143</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.531879024600919</v>
+        <v>-3.518456024749028</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.925454168689775</v>
+        <v>3.937169604027048</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.442520577690452</v>
+        <v>-3.42862640947093</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-10.98831225541132</v>
+        <v>-10.9722971210161</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-6.643672095189714</v>
+        <v>-6.628797267139646</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.159425730712279</v>
+        <v>-2.145810711098896</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.641293337977032</v>
+        <v>-3.627236593342495</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.410369333929658</v>
+        <v>-3.396236739981795</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.472256195667676</v>
+        <v>-3.458071550107483</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.021755784484974</v>
+        <v>-5.006894755939214</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.926955063237507</v>
+        <v>-5.911711262832448</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.097165991902841</v>
+        <v>-3.082745613149037</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.7202178056447863</v>
+        <v>-0.7066617592931834</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.869097871969892</v>
+        <v>-1.879527507668044</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>130</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.887779468586544</v>
+        <v>-2.874355249884374</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.809432427877283</v>
+        <v>-6.794425845823568</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.60440720784608</v>
+        <v>-2.590567197939919</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1718976974863793</v>
+        <v>-0.1587942219023333</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.8233129230760454</v>
+        <v>0.8361895518700067</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.718775703672904</v>
+        <v>-2.704814995581565</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.804816391960287</v>
+        <v>-2.790803892776324</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.202418759187303</v>
+        <v>-0.189054932266906</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5045277164096973</v>
+        <v>0.5177121796863844</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.12151951657038</v>
+        <v>-1.107594100970211</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.637880600138217</v>
+        <v>-3.623052605223549</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.167096061832908</v>
+        <v>-3.588916918858267</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.028033942606797</v>
+        <v>1.0415899889584</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.568398571270933</v>
+        <v>-2.578828206969085</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>113</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.808931988598061</v>
+        <v>-3.795275084912561</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.886948131405866</v>
+        <v>-1.873461748070682</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.281790320920813</v>
+        <v>-2.268119584588547</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.035550353811516</v>
+        <v>-3.02166622152324</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.574368985688537</v>
+        <v>-3.560256159143393</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.044963936012138</v>
+        <v>-5.030331487996946</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-5.131221790494024</v>
+        <v>-5.116535310828858</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-7.36786834332085</v>
+        <v>-7.352363225371327</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.777975244294673</v>
+        <v>-4.763258588296964</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.975283370407176</v>
+        <v>-2.960869263659959</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.411145658933279</v>
+        <v>-1.397053545248895</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.26171825380024</v>
+        <v>-2.24826596508013</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.336840121382103</v>
+        <v>-5.3232840750305</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.2226157241683211</v>
+        <v>0.212186088470169</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>120</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.430176765723715</v>
+        <v>-0.4173959515460623</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4419259491569605</v>
+        <v>0.4548416032297169</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.04552215676081772</v>
+        <v>0.05862993831681251</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.334936673518072</v>
+        <v>4.346623507714334</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.195902013589887</v>
+        <v>-1.182342704829722</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.093635595202564</v>
+        <v>4.105543421357481</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6795104679451001</v>
+        <v>0.6925655148339658</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.457120361573537</v>
+        <v>-1.44322451310871</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.685534714451272</v>
+        <v>-0.6718930062666715</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.622655513371008</v>
+        <v>2.635463654053403</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.221597703898581</v>
+        <v>5.760481403168178</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5.422647527910684</v>
+        <v>5.436099816630794</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.669059583632439</v>
+        <v>6.682615629984042</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.252114249242069</v>
+        <v>5.241684613543917</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>123</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-6.132697366246077</v>
+        <v>-6.118099178277134</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.309523455779726</v>
+        <v>-5.294798889743568</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.65026818491036</v>
+        <v>-1.636728007337418</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.200560030909081</v>
+        <v>-7.185196549326299</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-6.92891990912117</v>
+        <v>-6.913520848503758</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-9.069559834227256</v>
+        <v>-9.053405057053467</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-13.21808929984361</v>
+        <v>-13.20044180067163</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-12.87701329370617</v>
+        <v>-12.85931172022163</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-16.19349172286415</v>
+        <v>-16.17466748507071</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-13.79722620755619</v>
+        <v>-13.77901103685481</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-8.310922621304854</v>
+        <v>-8.297465327594637</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.837515073715515</v>
+        <v>-5.824062784995405</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-9.509802204985633</v>
+        <v>-9.49624615863403</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-10.07308900279045</v>
+        <v>-10.08351863848861</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>137</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.961836492212925</v>
+        <v>-3.9476836731898</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.486033695359481</v>
+        <v>-0.4727245293868663</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.33855692958339</v>
+        <v>-2.3245779783201</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.208914469823497</v>
+        <v>-2.194974104134815</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.022231177047765</v>
+        <v>-2.008232934207555</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.913328035718287</v>
+        <v>-3.89858678862317</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.731651303104258</v>
+        <v>-4.716473682572726</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.204994849470275</v>
+        <v>-5.189475882202132</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.538920676762594</v>
+        <v>-4.523605523348095</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-8.628393497331118</v>
+        <v>-9.030519857925313</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-7.373292807050156</v>
+        <v>-7.359835513339938</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-8.068836657003999</v>
+        <v>-8.055384368283889</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-7.75916426064979</v>
+        <v>-7.745608214298187</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.779515921074236</v>
+        <v>-6.789945556772388</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>112</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.594004016168029</v>
+        <v>-2.054035233285155</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3594942938770131</v>
+        <v>0.3723772329966835</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8558966171652571</v>
+        <v>0.8686255263544567</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.768659963100028</v>
+        <v>2.780683327517387</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.123400123355879</v>
+        <v>3.1354096315522</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.530234075503614</v>
+        <v>2.542576230980373</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.015267063467824</v>
+        <v>6.026473869495376</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10.01277393436444</v>
+        <v>10.02266866054327</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.276476213244088</v>
+        <v>7.287416491393756</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>7.319208171073299</v>
+        <v>7.33261329872613</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.114454846755933</v>
+        <v>7.127912140466151</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>8.934552289815443</v>
+        <v>8.948004578535553</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.728583393156249</v>
+        <v>6.742139439507852</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.406876154003768</v>
+        <v>3.396446518305616</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>120</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.008714303114061295</v>
+        <v>0.02123659278968404</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.049037157311005</v>
+        <v>5.060086524852885</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.3191234504853</v>
+        <v>6.329693072803394</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.619803649669386</v>
+        <v>5.630626199636168</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.916255753571988</v>
+        <v>5.927073566559841</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>12.87503765009967</v>
+        <v>12.88327054650603</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8.631930562823698</v>
+        <v>8.641944858875519</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>7.334953914448477</v>
+        <v>7.345598308860602</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.788190194249459</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.259684361549311</v>
+        <v>2.273089489202142</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.388264370565061</v>
+        <v>5.401721664275279</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.255980861244005</v>
+        <v>1.269433149964115</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.002392916965774816</v>
+        <v>0.01594896331737772</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.247885750757753</v>
+        <v>-2.258315386455905</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>122</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-9.079419381618827</v>
+        <v>-9.066897091943204</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-13.53281135672135</v>
+        <v>-13.96388682581304</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-10.66198032344722</v>
+        <v>-10.64450312615585</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-12.99042837405026</v>
+        <v>-12.9719988700349</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-11.89998987336799</v>
+        <v>-11.88190007863372</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-12.42568230227697</v>
+        <v>-12.40735100530189</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-9.242345725734985</v>
+        <v>-9.225103816253963</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-13.81625896097381</v>
+        <v>-13.79698320493873</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-13.42024509823132</v>
+        <v>-13.86630666455137</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-15.09004241440698</v>
+        <v>-15.07663728675415</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-18.57348426331453</v>
+        <v>-18.56002696960432</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-18.5391011059691</v>
+        <v>-18.52564881724899</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-14.04132293002876</v>
+        <v>-14.02776688367716</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-13.79160159775248</v>
+        <v>-13.80203123345063</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>117</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8943290870849836</v>
+        <v>0.9068513767606063</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.431328228240936</v>
+        <v>-2.418418418664885</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.357025857178257</v>
+        <v>-2.812666826107069</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3317256895645784</v>
+        <v>0.3447805158584814</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.061659058500233</v>
+        <v>4.073182892462981</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9447476409686573</v>
+        <v>0.9576606732970632</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.557042486685901</v>
+        <v>-2.542451464376811</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.171070909120822</v>
+        <v>-2.156393511439333</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.214976778208907</v>
+        <v>-8.201778039254144</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-7.355700253834925</v>
+        <v>-7.342295126182094</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.851051868750993</v>
+        <v>-5.837594575040775</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-6.671369566106414</v>
+        <v>-6.657917277386304</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.672820758247894</v>
+        <v>-3.659264711896292</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.713697716569897</v>
+        <v>-1.724127352268049</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>125</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.274824097726992</v>
+        <v>2.287346387402614</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.9428647035733775</v>
+        <v>-0.9299548939973263</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.5386612123205197</v>
+        <v>-0.5256540809029175</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.759770117169801</v>
+        <v>-5.185876728091955</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.305857996120054</v>
+        <v>-1.292061717919502</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.38876417013919</v>
+        <v>1.401460303010992</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.493196059648859</v>
+        <v>-3.478009351611185</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.562523900573609</v>
+        <v>-5.546132539887417</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.423523786755908</v>
+        <v>-2.410325047801145</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.873648971783837</v>
+        <v>-4.860243844131006</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-8.278402296101419</v>
+        <v>-8.264945002391201</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-11.44401913875598</v>
+        <v>-11.43056685003587</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-10.26427374970088</v>
+        <v>-10.25071770334928</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-9.214552417424784</v>
+        <v>-9.224982053122936</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>90</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2448858182332856</v>
+        <v>0.2574081079089083</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.711134683303975</v>
+        <v>-4.698224873727924</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-8.433256771873616</v>
+        <v>-8.420249640456014</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.085275577094549</v>
+        <v>-6.072296434696085</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-8.229071916459219</v>
+        <v>-8.829195768250521</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.715642049265902</v>
+        <v>-5.69960155289133</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-8.024151112794364</v>
+        <v>-8.006590843307045</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.051412789462745</v>
+        <v>-4.035412326662708</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.7790793423117179</v>
+        <v>-0.7658806033569547</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.629204527339397</v>
+        <v>-1.615799399686566</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.499375481676353</v>
+        <v>1.51283277538657</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4226475279106765</v>
+        <v>0.4360998166307866</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.330940416367554</v>
+        <v>-3.317384370015951</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.081219084091018</v>
+        <v>-3.09164871978917</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>117</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.914534688982357</v>
+        <v>-2.902012399306734</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.963076861368073</v>
+        <v>-1.950167051792022</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.357945567964663</v>
+        <v>-2.344938436547061</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.374211420125249</v>
+        <v>-1.361232277726785</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.472788081461118</v>
+        <v>-4.459677277086179</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.470418935625915</v>
+        <v>-2.455700716276922</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.702082177217733</v>
+        <v>-1.687239552786025</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.880472618522134</v>
+        <v>-3.864264043415908</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.041433478201547</v>
+        <v>2.054632217156311</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.227495125629794</v>
+        <v>-2.214089997976963</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7228467405456698</v>
+        <v>-0.709389446835452</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.020938126201088</v>
+        <v>1.034390414921198</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.382222467649413</v>
+        <v>-5.36866642129781</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.568398571270556</v>
+        <v>-2.578828206968709</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>107</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.39331180183607</v>
+        <v>-4.380789512160447</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-6.019884458547359</v>
+        <v>-6.006974648971308</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.854666618862126</v>
+        <v>3.867673750279728</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.616581948897348</v>
+        <v>-1.603602806498884</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.577664742525464</v>
+        <v>1.590775546900403</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9248908596433694</v>
+        <v>-0.9105180731275553</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.521644053846735</v>
+        <v>5.533131721500411</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.9122424545665737</v>
+        <v>0.3867324406316683</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.654980886141502</v>
+        <v>3.668179625096265</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>7.477752897374614</v>
+        <v>7.491158025027445</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.403840694552571</v>
+        <v>5.417297988262789</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.972991101372813</v>
+        <v>-2.959538812652703</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.327825151570266</v>
+        <v>-4.314269105218663</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.27436550153697</v>
+        <v>-1.284795137235122</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>92</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>5.60997918996658</v>
+        <v>5.622501479642203</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.151339503437136</v>
+        <v>6.164249313013187</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3307725385949993</v>
+        <v>0.3437796700126015</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.801309478317265</v>
+        <v>-2.788330335918801</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.426077934567054</v>
+        <v>-4.412967130192115</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-4.607320047162609</v>
+        <v>-5.200842533072475</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.608383980052977</v>
+        <v>-3.592251836359857</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-9.571349873712684</v>
+        <v>-9.558151134757921</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-10.42147505874011</v>
+        <v>-10.40806993108728</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-10.62622838305794</v>
+        <v>-10.61277108934772</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-9.504888703972881</v>
+        <v>-9.491436415252771</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-7.751230271439773</v>
+        <v>-7.73767422508817</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-5.327595895685221</v>
+        <v>-5.338025531383373</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>108</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.994289507720396</v>
+        <v>-2.981767218044773</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.8579717904597</v>
+        <v>1.870881600035752</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.015264296970663</v>
+        <v>-5.002257165553061</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.03783046348277</v>
+        <v>-3.024851321084306</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-8.206400324959297</v>
+        <v>-8.193289520584358</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.426957888987324</v>
+        <v>-1.413914992692959</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.769414575866293</v>
+        <v>-4.282631331032633</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.310672048721763</v>
+        <v>-3.297491039426525</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.297597860829981</v>
+        <v>-4.284399121875218</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.295871194006061</v>
+        <v>-3.28246606635323</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.426550444249571</v>
+        <v>-4.413093150539353</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.392167286904353</v>
+        <v>-4.378714998184243</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.960570045997393</v>
+        <v>-2.94701399964579</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.710848713721106</v>
+        <v>-2.721278349419258</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>136</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.49343832020989</v>
+        <v>-2.480916030534267</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.306752772708208</v>
+        <v>0.3196625822842591</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.08811593388847427</v>
+        <v>-0.07510880247087215</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.899039271869206</v>
+        <v>-2.886060129470742</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-6.37863695752953</v>
+        <v>-6.36552615315459</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.81648913746109</v>
+        <v>-6.803446241166725</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-7.636516972380264</v>
+        <v>-7.623450718079788</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-8.10370037116185</v>
+        <v>-8.090519361866612</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-8.164700257344151</v>
+        <v>-8.151501518389388</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.867766618842658</v>
+        <v>-3.854361491189827</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.866637590219071</v>
+        <v>-1.853180296508853</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.302842668167749</v>
+        <v>-3.289390379447639</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.423961544416763</v>
+        <v>1.437517590768365</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-4.208670064483513</v>
+        <v>-4.219099700181665</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>138</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.30366312906547</v>
+        <v>3.316185418741092</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.829649614333647</v>
+        <v>-4.816739804757596</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-8.847706726727345</v>
+        <v>-8.834699595309743</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.195714463685064</v>
+        <v>-2.1827353212866</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5602226352788833</v>
+        <v>-0.547111830903944</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.436693741041573</v>
+        <v>-2.423650844747208</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-5.419978182951525</v>
+        <v>-5.406911928651049</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.713248538254774</v>
+        <v>-3.700067528959536</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-7.39743683023417</v>
+        <v>-7.384238091279407</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-8.972199696421519</v>
+        <v>-8.958794568768688</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-12.8001414265362</v>
+        <v>-12.78668413282598</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-12.04112058803135</v>
+        <v>-12.02766829931124</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-8.113549112019811</v>
+        <v>-8.099993065668208</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-8.588465460902775</v>
+        <v>-8.598895096600927</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>151</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.82456414802455</v>
+        <v>-2.812041858348927</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.449382794101389</v>
+        <v>-2.436472984525338</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1952448781814198</v>
+        <v>-0.1822377467638177</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.700753334977968</v>
+        <v>-4.687774192579504</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.252419583162727</v>
+        <v>-3.239308778787787</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.279480956705257</v>
+        <v>-4.266438060410891</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-6.350969640864882</v>
+        <v>-6.337903386564406</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-8.804908006533879</v>
+        <v>-8.791726997238641</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-10.19041120397446</v>
+        <v>-10.17721246501969</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-7.729278110856683</v>
+        <v>-7.715872983203852</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.622773157028575</v>
+        <v>-4.609315863318358</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.588389999683145</v>
+        <v>-4.574937710963034</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.359637988111331</v>
+        <v>-2.346081941759728</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7854133445768454</v>
+        <v>-0.7958429802749976</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>147</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.248058278429482</v>
+        <v>1.260580568105105</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.718117318526446</v>
+        <v>3.731027128102497</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.003520720773395</v>
+        <v>4.016527852190997</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.453501744537434</v>
+        <v>3.466480886935898</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.234808420621569</v>
+        <v>2.247919224996508</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.171706140650151</v>
+        <v>1.184749036944517</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.488332967595568</v>
+        <v>4.501399221896044</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.102782221875373</v>
+        <v>8.11596323117061</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.041782335692993</v>
+        <v>8.054981074647756</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.232473477195825</v>
+        <v>9.245878604848656</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.707992261721699</v>
+        <v>9.721449555431917</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.961576590435008</v>
+        <v>7.975132636786611</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>9.571842140398445</v>
+        <v>9.561412504700293</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>173</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.575925841639666</v>
+        <v>3.588448131315289</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.276490956999176</v>
+        <v>4.289400766575227</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.9914488399979575</v>
+        <v>1.00445597141556</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.85580601884817</v>
+        <v>2.868785161246635</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.317384803776136</v>
+        <v>2.330495608151075</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.8807226952490197</v>
+        <v>0.8937655915433851</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.842231752543213</v>
+        <v>4.85529800684369</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.953083035842575</v>
+        <v>4.966264045137812</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.626187195903114</v>
+        <v>6.639385934857877</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.776062010874981</v>
+        <v>5.789467138527812</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.30541273280032</v>
+        <v>7.318870026510538</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.183726525983964</v>
+        <v>6.197178814704074</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.763471915039062</v>
+        <v>5.777027961390665</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.857123883153434</v>
+        <v>4.846694247455282</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>181</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.51761140354693</v>
+        <v>5.530133693222552</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.353551602737369</v>
+        <v>3.36646141231342</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.406196708295475</v>
+        <v>2.419203839713077</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.298880780129551</v>
+        <v>5.311859922528015</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.865431940747904</v>
+        <v>5.878542745122843</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.057901502772992</v>
+        <v>5.070944399067358</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.525653973345982</v>
+        <v>5.538720227646458</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.743553447492722</v>
+        <v>1.75673445678796</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.997470688382244</v>
+        <v>5.010669427337007</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.042373127663765</v>
+        <v>3.055778255316596</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.942592179036701</v>
+        <v>3.956049472746919</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.976975336382033</v>
+        <v>3.990427625102143</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.415654965170496</v>
+        <v>-1.402098918818893</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.165933632894244</v>
+        <v>-1.176363268592397</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>220</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.324743497971816</v>
+        <v>4.337265787647439</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.622260794098494</v>
+        <v>3.635170603674545</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.954664814774631</v>
+        <v>5.967671946192233</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.812190674654836</v>
+        <v>3.8251698170533</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.455587641400925</v>
+        <v>6.468698445775864</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.662120488207435</v>
+        <v>7.675163384501801</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.75920495275334</v>
+        <v>10.77227120705382</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.65565791760816</v>
+        <v>11.6688389269034</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>12.95829439506225</v>
+        <v>12.97149313401701</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>14.38089648276159</v>
+        <v>14.39430161041442</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.99432497662585</v>
+        <v>11.00778227033607</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>14.66507177033492</v>
+        <v>14.67852405905503</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>13.33572625029911</v>
+        <v>13.34928229665071</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>11.76726576439361</v>
+        <v>11.75683612869546</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>247</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.757573825539026</v>
+        <v>1.770096115214649</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>6.623733006097005</v>
+        <v>6.636642815673056</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.014289400715015</v>
+        <v>5.027296532132617</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.334825934132247</v>
+        <v>4.347805076530712</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.60612131825031</v>
+        <v>4.619232122625249</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.118138154751421</v>
+        <v>6.131181051045786</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.438262737074254</v>
+        <v>6.45132899137473</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>12.04395383221993</v>
+        <v>12.05713484151517</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.9829539460376</v>
+        <v>11.99615268499237</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>11.13282876100969</v>
+        <v>11.14623388866252</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.73779203588238</v>
+        <v>11.7512493295926</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.17703349282299</v>
+        <v>12.1904857815431</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.9713537806635</v>
+        <v>12.9849098270151</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.79192531536893</v>
+        <v>10.78149567967078</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>198</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.072218245446599</v>
+        <v>4.084740535122222</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.07470890287118</v>
+        <v>-1.061799093295129</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.459476599366802</v>
+        <v>-0.4464694679491998</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.206130068594256</v>
+        <v>3.21910921099272</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.6475068333200653</v>
+        <v>0.6606176376950046</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.37536656891497</v>
+        <v>2.388432823215446</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.908183170133462</v>
+        <v>1.9213641794287</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.3320317687996592</v>
+        <v>0.3452305077544224</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.53241163427677</v>
+        <v>4.545816761929601</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.832708815009696</v>
+        <v>4.846166108719913</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.382243487506642</v>
+        <v>6.395695776226752</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.982190896763747</v>
+        <v>7.99574694311535</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.231912229040049</v>
+        <v>8.221482593341896</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Stoch D-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Stoch D-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4079</v>
+        <v>4080</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1214199398095701</v>
+        <v>0.1210873899396248</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2582244393508262</v>
+        <v>0.2578490005464857</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2678455215983675</v>
+        <v>0.2674652841180603</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1180222849618886</v>
+        <v>0.1176792635970045</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1310902210130394</v>
+        <v>0.1307407321761289</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1728529659083549</v>
+        <v>0.1724948201894065</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1994221022215896</v>
+        <v>0.199056802178049</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1373537004055834</v>
+        <v>0.1370007210564239</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.16335182538905</v>
+        <v>0.1629919656627479</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1840047142313495</v>
+        <v>0.1836347063097321</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2625090218799642</v>
+        <v>0.2621184313584877</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2372354557061485</v>
+        <v>0.2368510823502135</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1984713483383231</v>
+        <v>0.1980938624434145</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2660065431049361</v>
+        <v>0.2661944174654778</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3973</v>
+        <v>3974</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.08500881694856588</v>
+        <v>-0.08563135533996302</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.02722021422818699</v>
+        <v>-0.02787733684454707</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.08220995703990042</v>
+        <v>-0.08285845189148944</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1642546726164937</v>
+        <v>-0.164881296491771</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1616901084735645</v>
+        <v>-0.1623243100272589</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.05145079356278615</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1476018083247723</v>
+        <v>-0.1482375732891796</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.09843744669072407</v>
+        <v>-0.09909163499697371</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.08064916447586512</v>
+        <v>0.07994889037426844</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1496349105395183</v>
+        <v>0.1489064826663764</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2356822109408299</v>
+        <v>0.2349292747020826</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2088110499232627</v>
+        <v>0.2080649407085886</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2305425562880359</v>
+        <v>0.2297854413048057</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2680551838842291</v>
+        <v>0.2685257475818261</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3845</v>
+        <v>3846</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2124637219725471</v>
+        <v>-0.2134892360280105</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.05625329887139685</v>
+        <v>0.05512441865168682</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.01336611694924983</v>
+        <v>-0.01448564213595915</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2321437198740881</v>
+        <v>-0.2332043813623699</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2375764855982325</v>
+        <v>-0.2386473860836418</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1595297017272017</v>
+        <v>-0.1606152634200697</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2820487053227438</v>
+        <v>-0.283104769163053</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.137854983409234</v>
+        <v>-0.1389586752866805</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.0232294599973315</v>
+        <v>0.02208211916847347</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.04482335869160181</v>
+        <v>0.04365225976508924</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2704542527551297</v>
+        <v>0.269219715717405</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1895654726295035</v>
+        <v>0.1883520688830345</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2520029013651524</v>
+        <v>0.2507639706824278</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1784254759434134</v>
+        <v>0.1792821174440675</v>
       </c>
     </row>
     <row r="9">
@@ -2373,46 +2373,46 @@
         <v>3697</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3500034320999674</v>
+        <v>-0.3515359766259962</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1406106386758594</v>
+        <v>-0.1422504115464136</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.06233005978700135</v>
+        <v>-0.06400403694006229</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3491202216803231</v>
+        <v>-0.3507136466639693</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3601404901167342</v>
+        <v>-0.3617484953025354</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2099588363556819</v>
+        <v>-0.2115989759447601</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3610169803230363</v>
+        <v>-0.3626198198458397</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1922375688610174</v>
+        <v>-0.1939013573869346</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.07626628878239217</v>
+        <v>-0.077964161793588</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.03445913632427278</v>
+        <v>0.03270400780090199</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2233549355828188</v>
+        <v>0.2215414840952832</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.1378088763873322</v>
+        <v>0.13601871362998</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2737841350705423</v>
+        <v>0.2719431944332982</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.144820046735525</v>
+        <v>0.1343904110373728</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3551</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2755831826468125</v>
+        <v>-0.2777164795941403</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.009000984545515678</v>
+        <v>0.006718763543872797</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2583076060629566</v>
+        <v>-0.2605325928800397</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4780849390262034</v>
+        <v>-0.4802438703828358</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.495457378784117</v>
+        <v>-0.4976353047669875</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.09837737771635346</v>
+        <v>-0.1006555127336171</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1677814466739989</v>
+        <v>-0.1700448406881563</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.08516806372410457</v>
+        <v>-0.08747562468669656</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.04625873329502639</v>
+        <v>-0.04858102529763642</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.008352039613846785</v>
+        <v>-0.0107221784022542</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1968229291238046</v>
+        <v>0.1943851411494606</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2189490392220463</v>
+        <v>0.21650522203619</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.3337549746021296</v>
+        <v>0.3473110209537325</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.2173822488665849</v>
+        <v>0.2069526131684327</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3408</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1389487033629422</v>
+        <v>-0.1417347439846424</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1553337588032591</v>
+        <v>-0.1582033227792223</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1246977307863375</v>
+        <v>-0.1275990788622892</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.03707481395488799</v>
+        <v>-0.03999633081694753</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2374777119865854</v>
+        <v>-0.2403711731298728</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.01189559529898077</v>
+        <v>-0.01484060857686131</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.02203256156357725</v>
+        <v>-0.02498075012783119</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.05435769379919009</v>
+        <v>0.05136030239287948</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.09749644191603579</v>
+        <v>0.09448151726333265</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2020108522630792</v>
+        <v>0.1989176920753835</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4537772286859081</v>
+        <v>0.4505975196029297</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3580935373003484</v>
+        <v>0.3549420968693724</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.3779797714258706</v>
+        <v>0.3915358177774735</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3049311506505106</v>
+        <v>0.2945015149523584</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>3278</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.02993467057493859</v>
+        <v>-0.03336358298190589</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1085566704156662</v>
+        <v>0.1049781683726181</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.02635659838311</v>
+        <v>-0.02992188072924762</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.03172796378432707</v>
+        <v>-0.03528500505700549</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2795468951952955</v>
+        <v>-0.2830657717418319</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.09545474456941605</v>
+        <v>0.09183927864420127</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.08832799302812333</v>
+        <v>0.08470717194181532</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.06454101865832484</v>
+        <v>0.06089476868505983</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.08135426202458262</v>
+        <v>0.07769689672795721</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2544998540777073</v>
+        <v>0.2507317656250905</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6160455379437266</v>
+        <v>0.6121516734245986</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.4978966635625</v>
+        <v>0.51134895228261</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3521997097255891</v>
+        <v>0.365755756077192</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4188826039298803</v>
+        <v>0.4084529682317282</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>3165</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1049868766404174</v>
+        <v>0.1009479493145093</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1798021815075543</v>
+        <v>0.1756144118348928</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.05416915537573175</v>
+        <v>0.04998849542749895</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.07551751175218868</v>
+        <v>0.0713377682323042</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.161911856893326</v>
+        <v>-0.1660602381631975</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2789831208429447</v>
+        <v>0.2747161496174826</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.274681587194948</v>
+        <v>0.2704071405209802</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3299003418506317</v>
+        <v>0.3255703305581719</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2548469110653642</v>
+        <v>0.2505335380574394</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3698128096438325</v>
+        <v>0.3653955622472722</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6884223484483414</v>
+        <v>0.6838863305209983</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.596423199316682</v>
+        <v>0.609875488036792</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5553155078030514</v>
+        <v>0.5688715541546543</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4258899206480677</v>
+        <v>0.4154602849499156</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3045</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1260770694429425</v>
+        <v>0.1213752951612292</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1694721808120079</v>
+        <v>0.1646103845878102</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.05450992379405761</v>
+        <v>0.04964794595402111</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.09234137147010557</v>
+        <v>-0.09714639884087717</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1211634763338552</v>
+        <v>-0.1260096976048999</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1286519888484818</v>
+        <v>0.1237475871843756</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2587277396777026</v>
+        <v>0.2537703572968226</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4003248030693172</v>
+        <v>0.3952765312938098</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2919062854699561</v>
+        <v>0.2868853230554294</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2810308311718259</v>
+        <v>0.2759347507475169</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4703661768049869</v>
+        <v>0.4838234705152047</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4062271666627311</v>
+        <v>0.4196794553828411</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.3143797806767736</v>
+        <v>0.3279358270283765</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2356938879941168</v>
+        <v>0.2252642522959647</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>2922</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3895367736146582</v>
+        <v>0.3840225779240356</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.4001075207506801</v>
+        <v>0.3944212472650008</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1262716306286293</v>
+        <v>0.1206350240699905</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2068752250771198</v>
+        <v>0.2012212152965986</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1654053262783464</v>
+        <v>0.1597068908826174</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.515845710353716</v>
+        <v>0.5100548340157403</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.8260270195754131</v>
+        <v>0.8201180970059738</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.9592271254181881</v>
+        <v>0.9532212112857295</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9858501441370038</v>
+        <v>0.9798254309950281</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8736474005638684</v>
+        <v>0.8675700457081987</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8400097504420501</v>
+        <v>0.8534670441522678</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.669054098752575</v>
+        <v>0.6825063874726851</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7279233755557826</v>
+        <v>0.7414794219073855</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.6696364942797146</v>
+        <v>0.6592068585815625</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2785</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6035899647882275</v>
+        <v>0.5971083073325048</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4436986685449611</v>
+        <v>0.4370779694916891</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2475217249730051</v>
+        <v>0.2409201879218514</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3257129946287876</v>
+        <v>0.3190950963601935</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2730197610918665</v>
+        <v>0.2663524047200951</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.7337260705734252</v>
+        <v>0.7269251759552517</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.099420890385865</v>
+        <v>1.092474676468193</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.262458152549144</v>
+        <v>1.255393384286755</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.25762522581141</v>
+        <v>1.250550759808327</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.341072751735005</v>
+        <v>1.354477879387836</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.244039355604151</v>
+        <v>1.257496649314369</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.098889299305057</v>
+        <v>1.112341588025167</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.145421043835917</v>
+        <v>1.15897709018752</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.036075948823154</v>
+        <v>1.025646313125002</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>2673</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6956702213789825</v>
+        <v>0.7081925110546052</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4472268727959232</v>
+        <v>0.4397889618177047</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2220305211100992</v>
+        <v>0.2146190289602146</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2233523285349648</v>
+        <v>0.2159533522937451</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1535874376449726</v>
+        <v>0.1461375115643904</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.6584515114442908</v>
+        <v>0.6508485137170084</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.8934445449368624</v>
+        <v>0.8857377106548583</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.8958156656193594</v>
+        <v>0.8880402862917123</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.005432442200316</v>
+        <v>0.9976031496558448</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.090585970228872</v>
+        <v>1.103991097881703</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9980660914780728</v>
+        <v>1.011523385188291</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7705712091676915</v>
+        <v>0.7840234978878016</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9114838260566884</v>
+        <v>0.9250398724082913</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9367382671994235</v>
+        <v>0.9263086315012714</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2553</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7279595712386779</v>
+        <v>0.7404818609143007</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2309255668257677</v>
+        <v>0.2226186885845536</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.0645543404351514</v>
+        <v>-0.07281100835321297</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.03029990747606348</v>
+        <v>-0.038555359684743</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1172782881330292</v>
+        <v>-0.1255868623484346</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.08422889623134466</v>
+        <v>0.07588155565407817</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5297084218869585</v>
+        <v>0.521168632007587</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5931534682595938</v>
+        <v>0.584512294631601</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.8281800910349233</v>
+        <v>0.8194321957384005</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.035634224455876</v>
+        <v>1.049039352108707</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.7917112957513055</v>
+        <v>0.8051685894615233</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7477552443227395</v>
+        <v>0.7612075330428496</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.9542143035697777</v>
+        <v>0.9677703499213806</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.08642682268507</v>
+        <v>1.075997186986918</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2431</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.220143953076857</v>
+        <v>1.232666242752479</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.9216602047002027</v>
+        <v>0.9345700142762539</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4672786377332869</v>
+        <v>0.4577305129844831</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.6201055523849277</v>
+        <v>0.610510912739251</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4740383771893235</v>
+        <v>0.4644049979505311</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7120401534168721</v>
+        <v>0.7023539425058374</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.020120024523678</v>
+        <v>1.010286377251482</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.316291401771096</v>
+        <v>1.306249213984778</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.543238862359672</v>
+        <v>1.556437601314435</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.844903064415263</v>
+        <v>1.858308192068094</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.763555745856621</v>
+        <v>1.777013039566839</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.715668232696089</v>
+        <v>1.729120521416199</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.706766974281017</v>
+        <v>1.72032302063262</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.833082300798353</v>
+        <v>1.8226526651002</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2314</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.236617738435996</v>
+        <v>1.249140028111619</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.091193327714073</v>
+        <v>1.104103137290124</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6100805503973561</v>
+        <v>0.6230876818149582</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6346865566848265</v>
+        <v>0.6239467193231079</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.2926418258870882</v>
+        <v>0.2819386999133897</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.700274044495707</v>
+        <v>0.689445175218637</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.200987791944385</v>
+        <v>1.18991918946864</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.492618709625184</v>
+        <v>1.481326655157915</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.036631788006403</v>
+        <v>2.049830526961166</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.31010210859646</v>
+        <v>2.323507236249291</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.14856399603341</v>
+        <v>2.162021289743628</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.139731941624312</v>
+        <v>2.153184230344422</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.978768601206625</v>
+        <v>1.992324647558227</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.012413874710226</v>
+        <v>2.001984239012074</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>2189</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.177332313624952</v>
+        <v>1.189854603300574</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.207345567965753</v>
+        <v>1.220255377541804</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6756779557604133</v>
+        <v>0.6886850871780155</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9427299939766627</v>
+        <v>0.9557091363751269</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.383922080684215</v>
+        <v>0.3718199480765279</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6609587106878365</v>
+        <v>0.6487864767380387</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.469043059851728</v>
+        <v>1.456475181992623</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.895493458951286</v>
+        <v>1.882620579041266</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.291323175327229</v>
+        <v>2.304521914281992</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.720320877462392</v>
+        <v>2.733726005115223</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.743982354423935</v>
+        <v>2.757439648134152</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.915414392536839</v>
+        <v>2.928866681256949</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.677891622615235</v>
+        <v>2.691447668966838</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.653515193356583</v>
+        <v>2.643085557658431</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>2099</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.217313344870902</v>
+        <v>1.229835634546525</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.461115564447077</v>
+        <v>1.474025374023128</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.066246857850487</v>
+        <v>1.079253989268089</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.2440737297539</v>
+        <v>1.257052872152364</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.7532262539776369</v>
+        <v>0.7663370583525762</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.934371797107957</v>
+        <v>0.9209898700999375</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.876088069636459</v>
+        <v>1.862228370309417</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.150482292851834</v>
+        <v>2.136371394435912</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.422974545783397</v>
+        <v>2.43617328473816</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.906817917210923</v>
+        <v>2.920223044863754</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.797348061211586</v>
+        <v>2.810805354921804</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.022298155193511</v>
+        <v>3.035750443913621</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.935535683362474</v>
+        <v>2.949091729714077</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.899406610684018</v>
+        <v>2.888976974985866</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1982</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.461221629412186</v>
+        <v>1.473743919087809</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.66325003156129</v>
+        <v>1.676159841137341</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.2683813249647</v>
+        <v>1.281388456382302</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.3986344575722</v>
+        <v>1.411613599970664</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.061724577512621</v>
+        <v>1.07483538188756</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.135360957415656</v>
+        <v>1.120320242756897</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.087312044854386</v>
+        <v>2.071758010572879</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.506497290142839</v>
+        <v>2.490596594349462</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.445497403960537</v>
+        <v>2.458696142915301</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.209902995925539</v>
+        <v>3.22330812357837</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.00514967160796</v>
+        <v>3.018606965318178</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.140441002515459</v>
+        <v>3.153893291235569</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.426543606504957</v>
+        <v>3.44009965285656</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.222178157751983</v>
+        <v>3.211748522053831</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1875</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.795320337222094</v>
+        <v>1.807842626897717</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.101700906463485</v>
+        <v>2.114610716039536</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.120790644192951</v>
+        <v>1.133797775610553</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.570702807168054</v>
+        <v>1.583681949566518</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.032281592095885</v>
+        <v>1.045392396470824</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.252932661109163</v>
+        <v>1.236213415983379</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.891326164874556</v>
+        <v>1.874228950802603</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.597476099426387</v>
+        <v>2.610657108721625</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.376476213244082</v>
+        <v>2.389674952198845</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.966351028216167</v>
+        <v>2.979756155868998</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.86826437056525</v>
+        <v>2.881721664275467</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.489314194577354</v>
+        <v>3.502766483297464</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.869059583632442</v>
+        <v>3.882615629984045</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.478780915908729</v>
+        <v>3.468351280210577</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1783</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.598489930911107</v>
+        <v>1.61101222058673</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.892745914359402</v>
+        <v>1.905655723935453</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.161554337807651</v>
+        <v>1.174561469225253</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.796291775347889</v>
+        <v>1.809270917746353</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.313924371934917</v>
+        <v>1.327035176309856</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.55531249799138</v>
+        <v>1.568355394285746</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.175102571679567</v>
+        <v>2.156290774929893</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.997879913223358</v>
+        <v>3.011060922518595</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.992965276620417</v>
+        <v>3.00616401557518</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.657141830235233</v>
+        <v>3.670546957888064</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.564559005076369</v>
+        <v>3.578016298786586</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.159794658215404</v>
+        <v>4.173246946935514</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.468648291802189</v>
+        <v>4.482204338153792</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.933176129967428</v>
+        <v>3.922746494269276</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1675</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.894621381282569</v>
+        <v>1.907143670958192</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.894988066825775</v>
+        <v>1.907897876401826</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.559820852766492</v>
+        <v>1.572827984184094</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.107984433135186</v>
+        <v>2.120963575533651</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.927772173286904</v>
+        <v>1.940882977661843</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.747602170704042</v>
+        <v>1.760645066998407</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.55839084149148</v>
+        <v>2.571457095791956</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.40464027853087</v>
+        <v>3.417821287826108</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.46304337742319</v>
+        <v>3.476242116377954</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.105455505828104</v>
+        <v>4.118860633480935</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.079806659122461</v>
+        <v>4.093263952832679</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.71120474184103</v>
+        <v>4.72465703056114</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.947666548806573</v>
+        <v>4.961222595158176</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.361566985560472</v>
+        <v>4.35113734986232</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1539</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.282390139829012</v>
+        <v>2.294912429504635</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.035338944018747</v>
+        <v>2.048248753594798</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.705447495381875</v>
+        <v>1.718454626799478</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.550450465546227</v>
+        <v>2.563429607944691</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.661801830071198</v>
+        <v>2.674912634446137</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.504402962068866</v>
+        <v>2.517445858363232</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.459305372152009</v>
+        <v>3.472371626452485</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.421621648484219</v>
+        <v>4.434802657779457</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.490576278221347</v>
+        <v>4.50377501717611</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.810041736468271</v>
+        <v>4.823446864121102</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.605288412150692</v>
+        <v>4.61874570586091</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.419398665012693</v>
+        <v>5.432850953732803</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.25905308590665</v>
+        <v>5.272609132258253</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.118910870424656</v>
+        <v>5.108481234726504</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>1401</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.181793656949189</v>
+        <v>2.194315946624812</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.711547667111276</v>
+        <v>2.724457476687327</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.74494448513996</v>
+        <v>2.757951616557563</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.017952792622545</v>
+        <v>3.030931935021009</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.979174689613181</v>
+        <v>2.99228549398812</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.991106277578673</v>
+        <v>3.004149173873039</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.333924309057281</v>
+        <v>4.346990563357757</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.222915071589128</v>
+        <v>5.236096080884366</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.661558297469639</v>
+        <v>5.674757036424403</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.16760727375506</v>
+        <v>6.181012401407891</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.319741886625202</v>
+        <v>6.33319918033542</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.139278505783629</v>
+        <v>7.152730794503739</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.576268719963643</v>
+        <v>6.589824766315246</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.469102115052202</v>
+        <v>6.45867247935405</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>1250</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.786561679790019</v>
+        <v>2.799083969465642</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.334988066825773</v>
+        <v>3.347897876401824</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.100119360229172</v>
+        <v>3.113126491646774</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.950372492836685</v>
+        <v>3.963351635235149</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.731951277764509</v>
+        <v>3.745062082139448</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.869393215480166</v>
+        <v>3.882436111774531</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.624659498207883</v>
+        <v>5.637725752508359</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6.917476099426388</v>
+        <v>6.930657108721626</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.576476213244085</v>
+        <v>7.589674952198848</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.846351028216162</v>
+        <v>7.859756155868993</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.641597703898583</v>
+        <v>7.655054997608801</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.555980861244009</v>
+        <v>8.569433149964119</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.655726250299104</v>
+        <v>7.669282296650707</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.345447582575389</v>
+        <v>7.335017946877237</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>1103</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.991602477614137</v>
+        <v>3.00412476728976</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.28392732339875</v>
+        <v>3.296837132974801</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.979720448171157</v>
+        <v>2.99272757958876</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.01659189446859</v>
+        <v>4.029571036867054</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.931479836241394</v>
+        <v>3.944590640616333</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.228921773957055</v>
+        <v>4.24196467025142</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.776101021326653</v>
+        <v>5.789167275627129</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.759506924449056</v>
+        <v>6.772687933744294</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.514463520587704</v>
+        <v>7.527662259542467</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.661618480618692</v>
+        <v>7.675023608271523</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.36620332493213</v>
+        <v>7.379660618642347</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.307204795967493</v>
+        <v>8.320657084687603</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.61496469091562</v>
+        <v>7.628520737267223</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.048729540870958</v>
+        <v>7.038299905172806</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>930</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.882905765811529</v>
+        <v>2.895428055487152</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.099289142094584</v>
+        <v>3.112198951670635</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.349581725820578</v>
+        <v>3.36258885723818</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.232523030471093</v>
+        <v>4.245502172869557</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.231736224001068</v>
+        <v>4.244847028376007</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.851758806878017</v>
+        <v>4.864801703172382</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.949820788530467</v>
+        <v>5.962887042830943</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.095540615555421</v>
+        <v>7.108721624850659</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.679702019695704</v>
+        <v>7.692900758650467</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.012372533592512</v>
+        <v>8.025777661245343</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.377511682393205</v>
+        <v>7.390968976103423</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.702217420383789</v>
+        <v>8.715669709103899</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.959382164277606</v>
+        <v>7.972938210629209</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.456415324510878</v>
+        <v>7.445985688812726</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>749</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.246214550284016</v>
+        <v>2.258736839959639</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.577555942338655</v>
+        <v>3.590563073756257</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.974831771875394</v>
+        <v>3.987810914273858</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.836944602197093</v>
+        <v>3.850055406572032</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.801943282235847</v>
+        <v>4.814986178530212</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.052323049609754</v>
+        <v>6.06538930391023</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.388877968585263</v>
+        <v>8.4020589778805</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.327878082402961</v>
+        <v>8.341076821357724</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.213400427415081</v>
+        <v>9.226805555067912</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.207579012309793</v>
+        <v>8.221036306020011</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9.84409835123067</v>
+        <v>9.85755063995078</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.22491183107348</v>
+        <v>10.23846787742508</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.540053724097433</v>
+        <v>9.529624088399281</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>529</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.381797974686059</v>
+        <v>1.394320264361681</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.794799030908941</v>
+        <v>2.807708840484992</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.588966241136553</v>
+        <v>2.601973372554156</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.042470791513431</v>
+        <v>4.055449933911895</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.747905909144464</v>
+        <v>2.761016713519403</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3.612455597332719</v>
+        <v>3.625498493627084</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.094829630533027</v>
+        <v>4.107895884833503</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.030292734587078</v>
+        <v>7.043473743882316</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.402185097932175</v>
+        <v>6.415383836886939</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.064347247497828</v>
+        <v>7.077752375150659</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.048629840004445</v>
+        <v>7.062087133714662</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.839156664646666</v>
+        <v>7.852608953366776</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.93118938829533</v>
+        <v>8.944745434646933</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>8.61380297009903</v>
+        <v>8.603373334400878</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>282</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.052660970570173</v>
+        <v>1.065183260245796</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.558912642394084</v>
+        <v>-0.5460028328180329</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4646583673213698</v>
+        <v>0.4776654987389719</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.786400861631002</v>
+        <v>3.799380004029466</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.120320072090749</v>
+        <v>1.133430876465688</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.41776200980641</v>
+        <v>1.430804906100775</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.042248150690163</v>
+        <v>2.055314404990639</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.638894539142704</v>
+        <v>2.652075548437942</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.514064865726361</v>
+        <v>1.527263604681124</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.500819113322542</v>
+        <v>3.514224240975373</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.941455859926954</v>
+        <v>2.954913153637172</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.03966880450642</v>
+        <v>4.05312109322653</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>5.392463838951585</v>
+        <v>5.406019885303188</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.706014958461928</v>
+        <v>6.695585322763776</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.656892828730534</v>
+        <v>0.6698026383065852</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.154182016646203</v>
+        <v>5.167161159044667</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>4.913202739289694</v>
+        <v>4.92624563558406</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1.257040450588846</v>
+        <v>1.270106704889322</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.361285623235915</v>
+        <v>4.374466632531153</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.300285737053613</v>
+        <v>4.313484476008377</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-1.516497534196652</v>
+        <v>-1.503040240486435</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1.482114376851221</v>
+        <v>-1.468662088131111</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.7118927973199334</v>
+        <v>-0.6983367509683305</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>3.109257106384923</v>
+        <v>3.098827470686771</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Stoch D-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Stoch D-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.874390701162362</v>
+        <v>-4.861868411486739</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.485964314126619</v>
+        <v>-6.473054504550568</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.45226159215178</v>
+        <v>-10.43925446073418</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.988675126210936</v>
+        <v>-1.975695983812471</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.527096341283105</v>
+        <v>-2.513985536908166</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.420130594043641</v>
+        <v>-3.407087697749276</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.50486431131592</v>
+        <v>-3.491798057015444</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.591095329145041</v>
+        <v>-1.577914319849803</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.652095215327343</v>
+        <v>-1.63889647637258</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.50222040035527</v>
+        <v>-2.488815272702439</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-5.053542948279798</v>
+        <v>-5.040090659559688</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.09284517827232</v>
+        <v>-3.079289131920717</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.605028607900792</v>
+        <v>-7.615458243598944</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>190</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.243403785053189</v>
+        <v>2.255926074728812</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.26340911945735</v>
+        <v>3.276318929033401</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.86854041286076</v>
+        <v>2.881547544278362</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.104056703362993</v>
+        <v>5.117035845761457</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.105062082139447</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.284130057585436</v>
+        <v>3.297172953879802</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.830975287681575</v>
+        <v>5.844041541982051</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.311160309952704</v>
+        <v>4.324341319247942</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.092265686928293</v>
+        <v>1.105464425883056</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2841752875733192</v>
+        <v>-0.2707701599204881</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.067875980311946</v>
+        <v>-2.054418686601728</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.507177033492823</v>
+        <v>-1.493724744772713</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.927431644437725</v>
+        <v>-1.913875598086122</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.256657680582499</v>
+        <v>-3.267087316280652</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>318</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.852473629475561</v>
+        <v>2.864995919151184</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.9264346077062697</v>
+        <v>0.9393444172823209</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.8460313099147143</v>
+        <v>0.8590384413323164</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.806473121767496</v>
+        <v>3.81945226416596</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.896982724305389</v>
+        <v>3.910093528680328</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.251028435605953</v>
+        <v>3.264071331900318</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.05308717116386</v>
+        <v>5.066153425464336</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.013576728357208</v>
+        <v>3.026757737652446</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.380249798149748</v>
+        <v>1.393448537104511</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.159055430731883</v>
+        <v>1.172460558384714</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.561421164025951</v>
+        <v>-1.547963870315733</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.5836417802654239</v>
+        <v>-0.5701894915453138</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.318361800015353</v>
+        <v>-1.30480575366375</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.7541750589340381</v>
+        <v>-0.7646046946321903</v>
       </c>
     </row>
     <row r="9">
@@ -4064,49 +4064,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.966947118762185</v>
+        <v>2.979469408437808</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.21190455504847</v>
+        <v>2.224814364624521</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.9605047992013382</v>
+        <v>0.9735119306189404</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.446218317247819</v>
+        <v>3.459197459646283</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.55019538911354</v>
+        <v>3.563306193488479</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.562840752953399</v>
+        <v>2.575883649247764</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.977036371869559</v>
+        <v>3.990102626170035</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.439189161524894</v>
+        <v>2.452370170820132</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.735790988404688</v>
+        <v>1.748989727359451</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.8856658033767602</v>
+        <v>0.8990709310295912</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.6038840948166211</v>
+        <v>-0.5904268011064033</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.07289734946671445</v>
+        <v>0.08634963818682451</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.9897555484160918</v>
+        <v>-0.9761995020644889</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1913764517593606</v>
+        <v>-0.1080655649000519</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.741089367086445</v>
+        <v>1.753611656762068</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.7809815521677876</v>
+        <v>0.7938913617438388</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.851910891173809</v>
+        <v>1.864918022591411</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.285095619872514</v>
+        <v>3.298074762270979</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.398140202845944</v>
+        <v>3.411251007220883</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.252585397890599</v>
+        <v>1.265628294184964</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.819317478663919</v>
+        <v>1.832383732964395</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.18926763037102</v>
+        <v>1.202448639666258</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.128267744188719</v>
+        <v>1.141466483143482</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.9296083572063907</v>
+        <v>0.9430134848592218</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2523436641795911</v>
+        <v>-0.2388863704693733</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3808269563455582</v>
+        <v>-0.3673746676254481</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.036215022131557</v>
+        <v>-1.11325841996166</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.532199476248131</v>
+        <v>-0.4706590514914311</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.7430213891691508</v>
+        <v>0.7555436788447736</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.377154513325102</v>
+        <v>1.390064322901154</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.8501854104273292</v>
+        <v>0.8631925418449313</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5841373541312649</v>
+        <v>0.5971164965297291</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.498820498372169</v>
+        <v>1.511931302747108</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.6073588693771299</v>
+        <v>0.6204017656714953</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.7868259447072248</v>
+        <v>0.7998921990077008</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3196425459257242</v>
+        <v>0.332823555220962</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2586426597434226</v>
+        <v>0.2718413986981858</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1951813363809336</v>
+        <v>-0.1817762087281025</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.324637434806831</v>
+        <v>-1.311180141096614</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.8939530885578364</v>
+        <v>-0.8805007998377263</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.9764430618702065</v>
+        <v>-1.036450860548754</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.7854133445769236</v>
+        <v>-0.7371513652920711</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2092643824927194</v>
+        <v>0.2217866721683421</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1742673461050472</v>
+        <v>0.1871771556810984</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.3424617025715193</v>
+        <v>0.3554688339891214</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.4727148351790191</v>
+        <v>0.4856939775774833</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.398257584070819</v>
+        <v>1.411368388445759</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1191229452098952</v>
+        <v>0.1321658415042606</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2596144531628468</v>
+        <v>0.2726807074633228</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2428815048317929</v>
+        <v>0.2560625141270307</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2944942312621137</v>
+        <v>0.3076929702168769</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.3304057285405975</v>
+        <v>-0.3170006008877664</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.661285178984301</v>
+        <v>-1.647827885274083</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.227108203017551</v>
+        <v>-1.275611895080921</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.682332440445812</v>
+        <v>-0.7318901948938148</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.047320779006526</v>
+        <v>-1.007374829646459</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2456860724577297</v>
+        <v>-0.2331637827821069</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.05905788722018457</v>
+        <v>-0.04614807764413342</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>0.05858103710131957</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.0759269383911203</v>
+        <v>0.08890608078958451</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.836207022020254</v>
+        <v>0.8493178263951933</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.4647526386656864</v>
+        <v>-0.451709742371321</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3496861561377642</v>
+        <v>-0.3366199018372882</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6038883458238331</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2784688417009633</v>
+        <v>-0.2652701027462001</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.6290935272283988</v>
+        <v>-0.6156883995755678</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.633047650746768</v>
+        <v>-1.61959035703655</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.344019138755982</v>
+        <v>-1.385412004881033</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.208818294245432</v>
+        <v>-1.250717703349281</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.9035303733364231</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2652743273400944</v>
+        <v>-0.2527520376644716</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.005190186293660304</v>
+        <v>0.007719623282390842</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>0.05858103710131957</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.532333277150407</v>
+        <v>0.5453124195488712</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.6177979800818036</v>
+        <v>0.6309087844567429</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.02397432064951488</v>
+        <v>0.03701721694388027</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2390125160523624</v>
+        <v>-0.2259462617518864</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.706195914833863</v>
+        <v>-0.6930149055386252</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.3215630024421827</v>
+        <v>-0.3083642634874195</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2804225903221607</v>
+        <v>-0.2670174626693296</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.7922292363333554</v>
+        <v>-0.8282248597887119</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.6190191387559878</v>
+        <v>-0.6551877242553203</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.3640056531861404</v>
+        <v>-0.4007177033492866</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.242817175921914</v>
+        <v>-0.214079461523113</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.8468519748284464</v>
+        <v>-0.8343296851528237</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.530714744419214</v>
+        <v>-0.5178049348431628</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.1223705996101856</v>
+        <v>-0.1093634681925835</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2330813224243684</v>
+        <v>-0.2201021800259042</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.128932256372039</v>
+        <v>-0.1158214519970997</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.8756670254836791</v>
+        <v>-0.8626241291893137</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.522649738739901</v>
+        <v>-1.509583484439425</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.909511852380838</v>
+        <v>-1.8963308430856</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.890190453422576</v>
+        <v>-1.876991714467813</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.615817646482633</v>
+        <v>-1.602412518829802</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.535637022789516</v>
+        <v>-1.566149821668311</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.13541093280265</v>
+        <v>-1.166258168363854</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.269748789958534</v>
+        <v>-1.30075792861075</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.217130983097448</v>
+        <v>-1.191487689193607</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.15576659208272</v>
+        <v>-1.143244302407098</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.5258362281850779</v>
+        <v>-0.5129264186090268</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3422522955914999</v>
+        <v>-0.3292451641738978</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4289189026803086</v>
+        <v>-0.4159397602818444</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3165808986635454</v>
+        <v>-0.3034700942886062</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.17604423932822</v>
+        <v>-1.163001343033855</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.83923059579066</v>
+        <v>-1.826164341490184</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.234107414673389</v>
+        <v>-2.220926405378151</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.150494141058154</v>
+        <v>-2.137295402103391</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.310986164258509</v>
+        <v>-2.336454979344317</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.114752766774842</v>
+        <v>-2.14048769414228</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.823729283683519</v>
+        <v>-1.849683432222704</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.914455040491312</v>
+        <v>-1.940572775813052</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.770140225842596</v>
+        <v>-1.747679660084323</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.189090494123015</v>
+        <v>-1.210862554598528</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.4595269833414548</v>
+        <v>-0.4466171737654037</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2523890009748371</v>
+        <v>-0.2393818695572349</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1890255004743651</v>
+        <v>-0.1760463580759009</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.05855039447629906</v>
+        <v>-0.04543959010135978</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.8982322025800258</v>
+        <v>-0.8851893062856604</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.250524448280409</v>
+        <v>-1.237458193979933</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.316370054419764</v>
+        <v>-1.303189045124526</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.444259572709093</v>
+        <v>-1.43106083375433</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.589043884769112</v>
+        <v>-1.612083309013954</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.422407654440335</v>
+        <v>-1.445667893957463</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.016137101222469</v>
+        <v>-1.039676026191273</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.265212716837041</v>
+        <v>-1.288787408443113</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.380995370444737</v>
+        <v>-1.361266426026845</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.100249465720808</v>
+        <v>-1.119529891920493</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.04928437899466331</v>
+        <v>-0.03637456941861217</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2369614654923424</v>
+        <v>0.2499685969099446</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.243375588811908</v>
+        <v>0.2563547312103722</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3860689248233342</v>
+        <v>0.3991797291982735</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1262353207433335</v>
+        <v>0.1392782170376989</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.5157739383246138</v>
+        <v>-0.5027076840241378</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.6733598138863073</v>
+        <v>-0.6601788045910695</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.982037718644456</v>
+        <v>-0.9688389796896928</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.302893085786316</v>
+        <v>-1.323401738867844</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.9157240567957814</v>
+        <v>-0.9365682985498154</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.846996806249777</v>
+        <v>-0.8678886107302404</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.170791440576124</v>
+        <v>-1.191660631388991</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.445608318045721</v>
+        <v>-1.428085715444297</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.659625784269785</v>
+        <v>-1.676318329384927</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.9979923704584692</v>
+        <v>-1.015621387542971</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.5298000874117861</v>
+        <v>-0.516792955994184</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6872339513520416</v>
+        <v>-0.6742548089535774</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.47766897540005</v>
+        <v>-0.4645581710251108</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.755601030779907</v>
+        <v>-0.7425581344855416</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.128021744599934</v>
+        <v>-1.114955490299458</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.595205143381435</v>
+        <v>-1.582024134086197</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.855648139087521</v>
+        <v>-1.873155887847183</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.271805653811484</v>
+        <v>-2.289374529220247</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.157364832124479</v>
+        <v>-2.17508325123913</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.091770003807895</v>
+        <v>-2.109529386058938</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.076853091882079</v>
+        <v>-2.09477768028124</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.315245258071251</v>
+        <v>-2.299188631310869</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.497207840942337</v>
+        <v>-1.512132392213573</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.087770553863891</v>
+        <v>-1.103410685795275</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6454332004177203</v>
+        <v>-0.6614424738704585</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6229967794005233</v>
+        <v>-0.6100176370020591</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1910675901600243</v>
+        <v>-0.177956785785085</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.6483426335764335</v>
+        <v>-0.6352997372820681</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.218251553005047</v>
+        <v>-1.205185298704571</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.631526595991403</v>
+        <v>-1.618345586696165</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.256964994954402</v>
+        <v>-2.272319656965578</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.592807093748213</v>
+        <v>-2.608248159125615</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.39071331122021</v>
+        <v>-2.406337339142418</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.381242261392401</v>
+        <v>-2.396873545500242</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.177787263214405</v>
+        <v>-2.193667460237464</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.277180865234229</v>
+        <v>-2.262819890960593</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.257936555207451</v>
+        <v>-1.271238611179513</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.077766726312483</v>
+        <v>-1.091597837163491</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6381946226077773</v>
+        <v>-0.6523629129950024</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.8847790223148451</v>
+        <v>-0.8987987938410811</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2615840757708483</v>
+        <v>-0.248473271395909</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5196976936107447</v>
+        <v>-0.5066547973163793</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.362007168458774</v>
+        <v>-1.348940914158298</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.87969561774532</v>
+        <v>-1.866514608450082</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.267485383521958</v>
+        <v>-2.281032118508222</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.736945230631157</v>
+        <v>-2.75049144392888</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.762974880825745</v>
+        <v>-2.77657290936795</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.954545454545453</v>
+        <v>-2.968047881902343</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.689590205397096</v>
+        <v>-2.703349282296656</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.716477442753884</v>
+        <v>-2.70346306578098</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.191606111916826</v>
+        <v>-1.203807596799415</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.23477556076709</v>
+        <v>-1.247357668439072</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9767146166047951</v>
+        <v>-0.9895266680251922</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.110332480606104</v>
+        <v>-1.123057631174127</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6085318140229248</v>
+        <v>-0.6216399941521971</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.745872485002927</v>
+        <v>-0.7328295887085616</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.65186224092254</v>
+        <v>-1.638795986622064</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.974118103472165</v>
+        <v>-1.960937094176927</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.202740799805689</v>
+        <v>-2.215155965675542</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.688736012402792</v>
+        <v>-2.701133162642364</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.577386330934509</v>
+        <v>-2.589896646491781</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.807426689578833</v>
+        <v>-2.819826646842849</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.717542514834058</v>
+        <v>-2.730098148654228</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.732381874788949</v>
+        <v>-2.720381568861256</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.283944938192633</v>
+        <v>-1.29478464367304</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.27396170486373</v>
+        <v>-1.285164652123967</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.050817140456068</v>
+        <v>-1.062215974106643</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.1246549294668</v>
+        <v>-1.135999666729226</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.8156847533283127</v>
+        <v>-0.8272962359592739</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.838315975191982</v>
+        <v>-0.8252730788976166</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.65464548578845</v>
+        <v>-1.641579231487974</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.076104147487186</v>
+        <v>-2.062923138191948</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.975582341193238</v>
+        <v>-1.986731083466445</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.664037987802146</v>
+        <v>-2.67506543607977</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.478035995735119</v>
+        <v>-2.489201295297377</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.602241768165058</v>
+        <v>-2.613350732819761</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.860424070507484</v>
+        <v>-2.871514771603977</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.723584971298976</v>
+        <v>-2.712791402343655</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.427757589457471</v>
+        <v>-1.437437769664783</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.494045875732979</v>
+        <v>-1.504020348913535</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.8211692771238859</v>
+        <v>-0.831521027935473</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.146630991483882</v>
+        <v>-1.156822504947705</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7032556939130501</v>
+        <v>-0.7137532488710079</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.8415436036919388</v>
+        <v>-0.8285007073975734</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.318434183709329</v>
+        <v>-1.305367929408852</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.936717448960714</v>
+        <v>-1.946728512193403</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.712839094213393</v>
+        <v>-1.722966721733144</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.190577418555215</v>
+        <v>-2.200671231832708</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.109916918537039</v>
+        <v>-2.120093344450538</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.619564990284374</v>
+        <v>-2.629519272558802</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.929018179582933</v>
+        <v>-2.938927310336183</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.655811158683342</v>
+        <v>-2.646039283354298</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.155645678069504</v>
+        <v>-1.164576707508857</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.198278348899876</v>
+        <v>-1.207486738982794</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7760312673858891</v>
+        <v>-0.7854933326945002</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.209309382424941</v>
+        <v>-1.218573050957325</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8460721728217564</v>
+        <v>-0.8555909107446098</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9868112252404018</v>
+        <v>-0.9962238547246329</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.406693664758173</v>
+        <v>-1.393627410457697</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.061098921529187</v>
+        <v>-2.070164005647875</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.015976616944592</v>
+        <v>-2.025077772025789</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.508212730173099</v>
+        <v>-2.517266904927652</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.438704436260878</v>
+        <v>-2.44783090843147</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.885496888546079</v>
+        <v>-2.894435922633441</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.115344728281322</v>
+        <v>-3.124269340628885</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.759090232550655</v>
+        <v>-2.750055551652785</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.233942118690578</v>
+        <v>-1.241907237568732</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.065011933174233</v>
+        <v>-1.07330964059139</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9584640731441709</v>
+        <v>-0.9668735083532169</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.287161534385099</v>
+        <v>-1.29542387496894</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.163555330165011</v>
+        <v>-1.171959535154386</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.004837553750605</v>
+        <v>-1.01326272683179</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.508967756301125</v>
+        <v>-1.517210144927525</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.115210348047547</v>
+        <v>-2.123290787069955</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.114819414513633</v>
+        <v>-2.122915264320795</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.542348811270202</v>
+        <v>-2.550416327083269</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.524889650577535</v>
+        <v>-2.53300278730292</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.95084644799293</v>
+        <v>-2.958788447787782</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.108628912416847</v>
+        <v>-3.116581157164546</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.756996147328138</v>
+        <v>-2.748806882371447</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.298899071063225</v>
+        <v>-1.305783354264456</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9942380333259777</v>
+        <v>-1.001468828186731</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.9135428788600066</v>
+        <v>-0.9208644036491265</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.370386808605993</v>
+        <v>-1.377521230040003</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.4329252888895</v>
+        <v>-1.44011635369958</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.305135659899769</v>
+        <v>-1.312337910253568</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.825709182901953</v>
+        <v>-1.832730174543308</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.424881315022283</v>
+        <v>-2.431745019746636</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.427783961727378</v>
+        <v>-2.434659648561606</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.610939687156744</v>
+        <v>-2.617870318075475</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.490811888792706</v>
+        <v>-2.497821714719962</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.969076259852713</v>
+        <v>-2.97590373621783</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.873797559224698</v>
+        <v>-2.880725319495518</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.832235344253874</v>
+        <v>-2.824982053122753</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2762</v>
+        <v>2763</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.070014896786553</v>
+        <v>-1.076016895087662</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.185040772395574</v>
+        <v>-1.191201222697273</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.308391278068697</v>
+        <v>-1.314559160840602</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.411474549010364</v>
+        <v>-1.417593189864029</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.38946337398577</v>
+        <v>-1.395659418582049</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.36150931159564</v>
+        <v>-1.367682978806485</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.004838515515473</v>
+        <v>-2.010794103087299</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.489113495949333</v>
+        <v>-2.4949550256229</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.675637989863979</v>
+        <v>-2.681423313697096</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.928312746187309</v>
+        <v>-2.934114462128846</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.005346238235234</v>
+        <v>-3.011148906946516</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.422022033111993</v>
+        <v>-3.427673540813458</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.135500676953875</v>
+        <v>-3.141311046330479</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.11983844204444</v>
+        <v>-3.113364246390937</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.160560671542854</v>
+        <v>-1.165576092030761</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.250311078473381</v>
+        <v>-1.255465076434824</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.250906631562884</v>
+        <v>-1.256104277583994</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.5813962379194</v>
+        <v>-1.586470526187568</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.485735238320359</v>
+        <v>-1.490900969519807</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.512352761924831</v>
+        <v>-1.517481752701855</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.229587077134575</v>
+        <v>-2.234482395386195</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.815829827260828</v>
+        <v>-2.820575767990704</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.064510764137687</v>
+        <v>-3.069180820325982</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.176837178845894</v>
+        <v>-3.181559813973365</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.089101884578788</v>
+        <v>-3.093878838524212</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.482441094159071</v>
+        <v>-3.487082625070165</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.095296398980231</v>
+        <v>-3.10011736029611</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.998829794698885</v>
+        <v>-2.993273062045198</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.045341997398388</v>
+        <v>-1.049556238732144</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.012564016507568</v>
+        <v>-1.016931280773576</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.9993921995233492</v>
+        <v>-1.003800591686556</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.340311546251272</v>
+        <v>-1.344600171993768</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.307527379778662</v>
+        <v>-1.311876028609738</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.383748896644995</v>
+        <v>-1.388049388388382</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.907600038798961</v>
+        <v>-1.911739697296063</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.292334729014577</v>
+        <v>-2.296392125057309</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.531843525744492</v>
+        <v>-2.535830592484771</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.581481869956157</v>
+        <v>-2.585529325370814</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.474941636617245</v>
+        <v>-2.479044219101382</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.814887852015296</v>
+        <v>-2.818878962344073</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.564306418763287</v>
+        <v>-2.568418552467513</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.394944574287351</v>
+        <v>-2.390352846980974</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3233</v>
+        <v>3234</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.7990452210109638</v>
+        <v>-0.8024435944394952</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.7305897451927237</v>
+        <v>-0.7341230724583099</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.8932221934082989</v>
+        <v>-0.8967348334687841</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.116466853447633</v>
+        <v>-1.119903605208762</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.114094373068312</v>
+        <v>-1.11757128202953</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.262874603094339</v>
+        <v>-1.266286898712821</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.547192353643965</v>
+        <v>-1.550524787448438</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.905345759171951</v>
+        <v>-1.908602150537625</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.042547875699704</v>
+        <v>-2.04576808577584</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.13481671969857</v>
+        <v>-2.138069662537433</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.952073495112543</v>
+        <v>-1.955399126580261</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.333663651893552</v>
+        <v>-2.336870929145896</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.11881920424635</v>
+        <v>-2.12212419484851</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.006881523518011</v>
+        <v>-2.003213345639757</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4654254809920033</v>
+        <v>-0.468080557955588</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.5148192886908731</v>
+        <v>-0.5175471192211702</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.7188587419606023</v>
+        <v>-0.7215495153584683</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.7773377875371565</v>
+        <v>-0.7800060289984359</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7450338230242792</v>
+        <v>-0.747741656178313</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9285495080733028</v>
+        <v>-0.9311893629552301</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.17297861930161</v>
+        <v>-1.175553031828279</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.712231502912793</v>
+        <v>-1.714674665613366</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.669853122819084</v>
+        <v>-1.672313351894722</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.860658919121462</v>
+        <v>-1.863110179316742</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.639830449452312</v>
+        <v>-1.642358694608873</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.999288459599086</v>
+        <v>-2.001711128642846</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.081550470052285</v>
+        <v>-2.083972972670125</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.962296998561101</v>
+        <v>-1.9593890809412</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3634</v>
+        <v>3635</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1764654658090947</v>
+        <v>-0.1782844515869826</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2651874680069213</v>
+        <v>-0.2670404290547168</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3160671966981212</v>
+        <v>-0.3179212318858546</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5002531932225978</v>
+        <v>-0.5020530286880458</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3101898147416691</v>
+        <v>-0.3120619573775585</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.4096183166450444</v>
+        <v>-0.411453539611685</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4520007599629423</v>
+        <v>-0.4538283386503394</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.9042821423318586</v>
+        <v>-0.9060031494492051</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7854913602651195</v>
+        <v>-0.7872481247242291</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.8784867947634964</v>
+        <v>-0.8802493401463991</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.8755977868905305</v>
+        <v>-0.8773694114071375</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.9909938362257336</v>
+        <v>-0.9927334708772264</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.148455317788923</v>
+        <v>-1.150167648343782</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.131118185173641</v>
+        <v>-1.129246152159894</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3881</v>
+        <v>3882</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.05378757547448743</v>
+        <v>-0.05472861076542301</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.171895336283761</v>
+        <v>0.1708665461501511</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.02221596865671671</v>
+        <v>0.02121793783224035</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1933232152075348</v>
+        <v>-0.1942639865531461</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.001976984705386542</v>
+        <v>0.0009757290168650457</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.004975627411255346</v>
+        <v>0.00397852822697331</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.01427054294437369</v>
+        <v>-0.01526473347774981</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.08148453859779892</v>
+        <v>-0.08247046329483254</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.02609021221474705</v>
+        <v>0.0250750036524181</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1148330129678854</v>
+        <v>-0.1158279923553991</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.0734589387378719</v>
+        <v>-0.0744688119150112</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1533675806823283</v>
+        <v>-0.1543567573479265</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2500542752032047</v>
+        <v>-0.2510267427518045</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3722952672055939</v>
+        <v>-0.3714014245807675</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4079</v>
+        <v>4080</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1458578674733104</v>
+        <v>0.1455193469393805</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1115610318709841</v>
+        <v>0.1112214345640865</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.001103133658347133</v>
+        <v>-0.001417629594968162</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.02871285810487478</v>
+        <v>-0.02902000290666251</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.03324286289171141</v>
+        <v>0.03291730346495569</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.001578192235733411</v>
+        <v>0.001261943477082639</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1015268501413189</v>
+        <v>0.101185502936552</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.01495467959774999</v>
+        <v>0.01463165595608729</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.04092283420392562</v>
+        <v>0.04059294485490739</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1105293284855691</v>
+        <v>0.1101773115986688</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1645178410862371</v>
+        <v>0.164151250364128</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1637240614400355</v>
+        <v>0.1633576967549075</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1494517404951878</v>
+        <v>0.1490862662660035</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.04536422881221824</v>
+        <v>0.04560618217136181</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/stoch/stoch_d_14.xlsx
+++ b/workspaces/btc_daily_14days/stoch/stoch_d_14.xlsx
@@ -575,46 +575,46 @@
         <v>106</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.871090161082158</v>
+        <v>7.842060288974587</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10.96989112122573</v>
+        <v>10.96879492767827</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.40130044357</v>
+        <v>13.40124558615385</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.71103460126481</v>
+        <v>10.71061398398994</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.11791505025447</v>
+        <v>11.1664166764914</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.593032024004152</v>
+        <v>8.616986045107453</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.21931952016672</v>
+        <v>13.26730723593265</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.988236786680936</v>
+        <v>9.037444802198657</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.2763238637421</v>
+        <v>3.349497204381869</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.485615468184179</v>
+        <v>1.584863882938038</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.281455304495701</v>
+        <v>1.381287959313326</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.316059826537419</v>
+        <v>1.439694075932117</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.9900413676993125</v>
+        <v>-0.8413909840293456</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1787915317829061</v>
+        <v>0.3507902913495684</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>128</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.756098403458807</v>
+        <v>3.72704341293877</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.521820709020602</v>
+        <v>-2.52302551124648</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.137247720014493</v>
+        <v>-2.137416712615718</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.88801389422968</v>
+        <v>1.887537103876767</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.130945615854408</v>
+        <v>2.17938903069723</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.208154491733893</v>
+        <v>3.232079364385584</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.904100202733176</v>
+        <v>3.952042174136238</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.098788341207914</v>
+        <v>1.147961228994511</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.818664531448363</v>
+        <v>1.891828077749672</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.311466961403397</v>
+        <v>3.410715018888709</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.7953913201802862</v>
+        <v>-0.6955677182789088</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.8003751363420477</v>
+        <v>0.9240049334713447</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4005538085887679</v>
+        <v>-0.2519054151975055</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.950017946877246</v>
+        <v>3.122016706443908</v>
       </c>
     </row>
     <row r="8">
@@ -679,98 +679,98 @@
         <v>149</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.211737609547292</v>
+        <v>3.502705697166995</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.952404601486521</v>
+        <v>5.259403947328941</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.214168757802248</v>
+        <v>1.51908843180388</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.682444973134388</v>
+        <v>2.989903936097711</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.815747250038847</v>
+        <v>3.169038693147051</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.10439671781338</v>
+        <v>1.128307193481476</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.689829072275174</v>
+        <v>1.737755068339595</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.224283577898845</v>
+        <v>1.273451914182388</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.504438499817681</v>
+        <v>2.577598315475527</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.315301169239099</v>
+        <v>0.4145329429733096</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.452215838583037</v>
+        <v>1.552038365804222</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.486851494188556</v>
+        <v>1.610477471561779</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2747366347334008</v>
+        <v>-0.1260912503714309</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.293138752246378</v>
+        <v>0.7939965722154128</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 18.69</t>
+          <t>X ≈ 18.7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.146967716078841</v>
+        <v>-2.224304572729686</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.765466444050453</v>
+        <v>-3.853071515341789</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.715947347599901</v>
+        <v>5.247921714492172</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.799709808306638</v>
+        <v>4.031378016272676</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.943279315712942</v>
+        <v>3.899970287433916</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.909956769525415</v>
+        <v>-1.939065917341765</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.046412634838546</v>
+        <v>-4.346587309413849</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.782379280801685</v>
+        <v>-2.409240401331324</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.7926183925957915</v>
+        <v>-0.7144186132756545</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.088912139358264</v>
+        <v>1.180656552554105</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.8820358251954232</v>
+        <v>0.9771721025409406</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.821567528496345</v>
+        <v>-1.684088528885077</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.561146887580755</v>
+        <v>-1.399523610668503</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.63046150517755</v>
+        <v>-1.831214586072797</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>143</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.518456024749028</v>
+        <v>-3.916847372953264</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.937169604027048</v>
+        <v>3.564144966168726</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.42862640947093</v>
+        <v>-3.113612594295972</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-10.9722971210161</v>
+        <v>-11.36415643481719</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-6.628797267139646</v>
+        <v>-6.966795198393221</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.145810711098896</v>
+        <v>-1.805442176316348</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.627236593342495</v>
+        <v>-3.26306482907772</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.396236739981795</v>
+        <v>-3.033676184162822</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.458071550107483</v>
+        <v>-3.071138074769969</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.006894755939214</v>
+        <v>-4.906236845954552</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.911711262832448</v>
+        <v>-5.810132416788079</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.082745613149037</v>
+        <v>-2.958172627823409</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.7066617592931834</v>
+        <v>-0.5577154246880838</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.879527507668044</v>
+        <v>-1.707528748101552</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.874355249884374</v>
+        <v>-2.523907650571907</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.794425845823568</v>
+        <v>-6.40395027845063</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.590567197939919</v>
+        <v>-2.989781353616287</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1587942219023333</v>
+        <v>0.1901847321491772</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.8361895518700067</v>
+        <v>0.4616360615874342</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.704814995581565</v>
+        <v>-2.315836799478667</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.790803892776324</v>
+        <v>-2.376885335984184</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.189054932266906</v>
+        <v>0.2042044816356423</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5177121796863844</v>
+        <v>0.9293059083698978</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.107594100970211</v>
+        <v>-0.6634645357202302</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.623052605223549</v>
+        <v>-3.489706878738183</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.588916918858267</v>
+        <v>-3.432827490856653</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.0415899889584</v>
+        <v>0.7497606617599715</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.578828206969085</v>
+        <v>-2.8178687897393</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>113</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.795275084912561</v>
+        <v>-3.411650785905515</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.873461748070682</v>
+        <v>-1.473537441376727</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.268119584588547</v>
+        <v>-1.869580028416912</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.02166622152324</v>
+        <v>-3.026944464404458</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.560256159143393</v>
+        <v>-3.515935289746388</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.030331487996946</v>
+        <v>-5.011332567346521</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-5.116535310828858</v>
+        <v>-5.071931253103187</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-7.352363225371327</v>
+        <v>-7.305573687357608</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.763258588296964</v>
+        <v>-4.690128593193727</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.960869263659959</v>
+        <v>-2.860649716939882</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.397053545248895</v>
+        <v>-1.296004631633551</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.24826596508013</v>
+        <v>-2.122931908912129</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.3232840750305</v>
+        <v>-5.172857320303478</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.212186088470169</v>
+        <v>0.3841848480368313</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4173959515460623</v>
+        <v>-0.443131112586201</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4548416032297169</v>
+        <v>0.4517763650721776</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.05862993831681251</v>
+        <v>0.05836865724602802</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.346623507714334</v>
+        <v>4.316303995749095</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.182342704829722</v>
+        <v>-1.126476924276631</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.105543421357481</v>
+        <v>4.100242066411361</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6925655148339658</v>
+        <v>0.7371078600202807</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.44322451310871</v>
+        <v>-1.379469567813729</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6718930062666715</v>
+        <v>-0.590838097381905</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.635463654053403</v>
+        <v>2.714435200248587</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.760481403168178</v>
+        <v>5.81335995934824</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5.436099816630794</v>
+        <v>5.047220383155882</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.682615629984042</v>
+        <v>6.30599969512614</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.241684613543917</v>
+        <v>4.904041499832147</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>123</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-6.118099178277134</v>
+        <v>-6.587283933368035</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.294798889743568</v>
+        <v>-5.747714316163481</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.636728007337418</v>
+        <v>-2.083030430569814</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.185196549326299</v>
+        <v>-7.638129460856071</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-6.913520848503758</v>
+        <v>-7.318578061587274</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-9.053405057053467</v>
+        <v>-9.482666137056611</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-13.20044180067163</v>
+        <v>-13.60705120328605</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-12.85931172022163</v>
+        <v>-12.45260400625394</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-16.17466748507071</v>
+        <v>-15.73890376395525</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-13.77901103685481</v>
+        <v>-13.31900648442446</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-8.297465327594637</v>
+        <v>-7.839137997540938</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.824062784995405</v>
+        <v>-5.696211292928332</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-9.49624615863403</v>
+        <v>-9.344262080501977</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-10.08351863848861</v>
+        <v>-9.911519878921759</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.9476836731898</v>
+        <v>-3.953169241268256</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.4727245293868663</v>
+        <v>-0.4691771314825885</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.3245779783201</v>
+        <v>-2.311398503293475</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.194974104134815</v>
+        <v>-2.18156329015644</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.008232934207555</v>
+        <v>-1.946351663272317</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.89858678862317</v>
+        <v>-3.845898644298785</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.716473682572726</v>
+        <v>-4.63040515039355</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.189475882202132</v>
+        <v>-5.095822872119236</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.523605523348095</v>
+        <v>-4.408627681884525</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-9.030519857925313</v>
+        <v>-8.852538424360318</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-7.359835513339938</v>
+        <v>-7.60829444507543</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-8.055384368283889</v>
+        <v>-8.274393163236667</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-7.745608214298187</v>
+        <v>-7.948201032172655</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.789945556772388</v>
+        <v>-6.977620974715506</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>112</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.054035233285155</v>
+        <v>-2.088454172977315</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3723772329966835</v>
+        <v>-0.1154329211051746</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8686255263544567</v>
+        <v>0.3817574963706249</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.780683327517387</v>
+        <v>2.297301947070039</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.1354096315522</v>
+        <v>2.696597705080372</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.542576230980373</v>
+        <v>2.075634739346896</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.026473869495376</v>
+        <v>5.581401976770593</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10.02266866054327</v>
+        <v>9.572986188158417</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.287416491393756</v>
+        <v>6.858135151335311</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>7.33261329872613</v>
+        <v>6.918872256972605</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.127912140466151</v>
+        <v>7.606031547828763</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>8.948004578535553</v>
+        <v>9.450776974487717</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.742139439507852</v>
+        <v>6.888684732579499</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.396446518305616</v>
+        <v>3.568445277872478</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>120</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.02123659278968404</v>
+        <v>-0.009264376995872681</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.060086524852885</v>
+        <v>5.069772899074387</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.329693072803394</v>
+        <v>6.343904152981388</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.630626199636168</v>
+        <v>5.640721996853578</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.927073566559841</v>
+        <v>5.984655568714992</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>12.88327054650603</v>
+        <v>12.92157742655866</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8.641944858875519</v>
+        <v>8.695998154769221</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>7.345598308860602</v>
+        <v>7.397332227985622</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.788190194249459</v>
+        <v>4.861394057763206</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.273089489202142</v>
+        <v>2.37191370858082</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.401721664275279</v>
+        <v>5.49984871277384</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.269433149964115</v>
+        <v>1.392873801067509</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.01594896331737772</v>
+        <v>0.1649264014044221</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.258315386455905</v>
+        <v>-2.086316626889619</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-9.066897091943204</v>
+        <v>-8.656787719307474</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-13.96388682581304</v>
+        <v>-13.51333041724933</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-10.64450312615585</v>
+        <v>-11.02680588458929</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-12.9719988700349</v>
+        <v>-13.33499386173623</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-11.88190007863372</v>
+        <v>-12.2017187727604</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-12.40735100530189</v>
+        <v>-12.74098901214049</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-9.225103816253963</v>
+        <v>-9.553739525863421</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-13.79698320493873</v>
+        <v>-14.0887398814763</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-13.86630666455137</v>
+        <v>-14.12793469167139</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-15.07663728675415</v>
+        <v>-15.77334274950729</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-18.56002696960432</v>
+        <v>-19.22919826007449</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-18.52564881724899</v>
+        <v>-19.1703966081216</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-14.02776688367716</v>
+        <v>-14.69258507090257</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-13.80203123345063</v>
+        <v>-13.97656052932826</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.9068513767606063</v>
+        <v>0.8798664151262088</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.418418418664885</v>
+        <v>-2.398373655805351</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.812666826107069</v>
+        <v>-2.792111644120446</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3447805158584814</v>
+        <v>-0.119854721549828</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.073182892462981</v>
+        <v>3.628184273091662</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9576606732970632</v>
+        <v>0.5111392834360089</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.542451464376811</v>
+        <v>-2.939347314263827</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.156393511439333</v>
+        <v>-2.557722447528718</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.201778039254144</v>
+        <v>-8.526898446496034</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-7.342295126182094</v>
+        <v>-7.655811773073722</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.837594575040775</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-6.657917277386304</v>
+        <v>-6.954327856126277</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.659264711896292</v>
+        <v>-3.959655274215336</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.724127352268049</v>
+        <v>-2.015695157962874</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.287346387402614</v>
+        <v>2.251331722450011</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.9299548939973263</v>
+        <v>-0.9186857354396594</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.5256540809029175</v>
+        <v>-0.5187729301035731</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.185876728091955</v>
+        <v>-5.150793650793474</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.292061717919502</v>
+        <v>-1.671788823491781</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.401460303010992</v>
+        <v>0.9819490762797045</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.478009351611185</v>
+        <v>-3.840611774850522</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.546132539887417</v>
+        <v>-5.893746122535454</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.410325047801145</v>
+        <v>-2.756115557069066</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.860243844131006</v>
+        <v>-5.167245725185452</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-8.264945002391201</v>
+        <v>-8.54598934732509</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-11.43056685003587</v>
+        <v>-11.66242578456319</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-10.25071770334928</v>
+        <v>-10.47028212382543</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-9.224982053122936</v>
+        <v>-9.427586468159092</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>90</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2574081079089083</v>
+        <v>-0.2871910928063954</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.698224873727924</v>
+        <v>-5.2044000211542</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-8.420249640456014</v>
+        <v>-8.931471342801984</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.072296434696085</v>
+        <v>-5.468253968254224</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-8.829195768250521</v>
+        <v>-8.179725331427861</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.69960155289133</v>
+        <v>-6.795828701497825</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-8.006590843307045</v>
+        <v>-9.078707012946012</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.035412326662708</v>
+        <v>-5.1000953288844</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.7658806033569547</v>
+        <v>-1.803734604688117</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.615799399686566</v>
+        <v>-2.627563185503355</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.51283277538657</v>
+        <v>0.5016297002943944</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4360998166307866</v>
+        <v>-0.5513146734523318</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.317384370015951</v>
+        <v>-4.27980593334923</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.09164871978917</v>
+        <v>-4.030761071334119</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.902012399306734</v>
+        <v>-2.118202950748703</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.950167051792022</v>
+        <v>-1.550916028687098</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.344938436547061</v>
+        <v>-1.944654017001803</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.361232277726785</v>
+        <v>-1.814769975787122</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.459677277086179</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.455700716276922</v>
+        <v>-2.031233597919915</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.687239552786025</v>
+        <v>-1.244432060026547</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.864264043415908</v>
+        <v>-3.405180074647561</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.054632217156311</v>
+        <v>2.490050706046347</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.214089997976963</v>
+        <v>-1.723608383243025</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.709389446835452</v>
+        <v>-0.2328335765418217</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.034390414921198</v>
+        <v>1.520248415060166</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.36866642129781</v>
+        <v>-4.807112901334172</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.578828206968709</v>
+        <v>-2.015695157963059</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.380789512160447</v>
+        <v>-4.361963676739045</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-6.006974648971308</v>
+        <v>-5.945140761894478</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.867673750279728</v>
+        <v>3.846306434976007</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.603602806498884</v>
+        <v>-1.579365079364869</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.590775546900403</v>
+        <v>1.635089483386693</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9105180731275553</v>
+        <v>-0.8699027755723563</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.533131721500411</v>
+        <v>5.550922616683451</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3867324406316683</v>
+        <v>0.4554602266709011</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.668179625096265</v>
+        <v>3.196265395311883</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>7.491158025027445</v>
+        <v>7.002066444126527</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.417297988262789</v>
+        <v>4.946074144738382</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.959538812652703</v>
+        <v>-3.329092451229641</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.314269105218663</v>
+        <v>-4.650176303719611</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.284795137235122</v>
+        <v>-1.623353663926252</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>5.622501479642203</v>
+        <v>5.554404304145159</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.164249313013187</v>
+        <v>6.121764853398027</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3437796700126015</v>
+        <v>0.3516827790618109</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.788330335918801</v>
+        <v>-2.744239631336413</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.412967130192115</v>
+        <v>-4.30875758949275</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-5.200842533072475</v>
+        <v>-5.111240887878004</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.592251836359857</v>
+        <v>-4.09662815989892</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.637729737486808</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-9.558151134757921</v>
+        <v>-9.975777615440812</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-10.40806993108728</v>
+        <v>-10.79960619625604</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-10.61277108934772</v>
+        <v>-11.00374664379189</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-9.491436415252771</v>
+        <v>-9.870311089222689</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-7.73767422508817</v>
+        <v>-8.114931381378156</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-5.338025531383373</v>
+        <v>-5.71534888495394</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.981767218044773</v>
+        <v>-2.968827421217256</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.870881600035752</v>
+        <v>1.870013842250636</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.002257165553061</v>
+        <v>-4.945742494687813</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.024851321084306</v>
+        <v>-2.980996068152031</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-8.193289520584358</v>
+        <v>-8.057401172406706</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.413914992692959</v>
+        <v>-1.36259730496382</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.282631331032633</v>
+        <v>-4.175546972171141</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.297491039426525</v>
+        <v>-3.723948539893826</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.284399121875218</v>
+        <v>-4.678352341691181</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.28246606635323</v>
+        <v>-3.667318537185061</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.413093150539353</v>
+        <v>-4.788890177381695</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.378714998184243</v>
+        <v>-4.730723440016803</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.94701399964579</v>
+        <v>-3.29101898125932</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.721278349419258</v>
+        <v>-3.041974119244159</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>136</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.480916030534267</v>
+        <v>-2.510111824886899</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.3196625822842591</v>
+        <v>0.3184757958396034</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.07510880247087215</v>
+        <v>-0.0752621924751935</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.886060129470742</v>
+        <v>-2.886554621848745</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-6.36552615315459</v>
+        <v>-6.316980233388819</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.803446241166725</v>
+        <v>-6.779488832217112</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-7.623450718079788</v>
+        <v>-7.575439039089467</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-8.090519361866612</v>
+        <v>-8.041271799472895</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-8.151501518389388</v>
+        <v>-8.078244408609692</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.854361491189827</v>
+        <v>-3.755014165895254</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.853180296508853</v>
+        <v>-1.753272260490178</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.289390379447639</v>
+        <v>-3.165693758419394</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.437517590768365</v>
+        <v>1.586207138546193</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-4.219099700181665</v>
+        <v>-4.047100940615003</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>138</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.316185418741092</v>
+        <v>3.286989624388461</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.816739804757596</v>
+        <v>-4.817926591202252</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-8.834699595309743</v>
+        <v>-8.834852985314065</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.1827353212866</v>
+        <v>-2.183229813664603</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.547111830903944</v>
+        <v>-0.4985659111381722</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.423650844747208</v>
+        <v>-2.399693435797595</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-5.406911928651049</v>
+        <v>-5.358900249660728</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.700067528959536</v>
+        <v>-3.65081996656582</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-7.384238091279407</v>
+        <v>-7.310980981499711</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-8.958794568768688</v>
+        <v>-8.859447243474115</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-12.78668413282598</v>
+        <v>-12.68677609680731</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-12.02766829931124</v>
+        <v>-11.90397167828299</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-8.099993065668208</v>
+        <v>-7.951303517890381</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-8.598895096600927</v>
+        <v>-8.426896337034265</v>
       </c>
     </row>
     <row r="28">
@@ -1719,98 +1719,98 @@
         <v>151</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.812041858348927</v>
+        <v>-2.841237652701558</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.436472984525338</v>
+        <v>-2.437659770969994</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1822377467638177</v>
+        <v>-0.182391136768139</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.687774192579504</v>
+        <v>-4.688268684957507</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.239308778787787</v>
+        <v>-3.190762859022016</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.266438060410891</v>
+        <v>-4.242480651461278</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-6.337903386564406</v>
+        <v>-6.289891707574085</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-8.791726997238641</v>
+        <v>-8.742479434844924</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-10.17721246501969</v>
+        <v>-10.10395535524</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-7.715872983203852</v>
+        <v>-7.616525657909278</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.609315863318358</v>
+        <v>-4.509407827299682</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.574937710963034</v>
+        <v>-4.45124108993479</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.346081941759728</v>
+        <v>-2.1973923939819</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7958429802749976</v>
+        <v>-0.6238442207083352</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 78.93</t>
+          <t>X ≈ 78.92</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>147</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.260580568105105</v>
+        <v>1.231384773752474</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.731027128102497</v>
+        <v>3.729840341657841</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.016527852190997</v>
+        <v>4.016374462186675</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.466480886935898</v>
+        <v>3.465986394557895</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.247919224996508</v>
+        <v>2.29646514476228</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.184749036944517</v>
+        <v>1.20870644589413</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.501399221896044</v>
+        <v>4.549410900886365</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.11596323117061</v>
+        <v>8.165210793564327</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.054981074647756</v>
+        <v>8.128238184427452</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.245878604848656</v>
+        <v>9.345225930143229</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.721449555431917</v>
+        <v>9.821357591450592</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.975132636786611</v>
+        <v>8.123822184564439</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>9.561412504700293</v>
+        <v>9.733411264266955</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>173</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.588448131315289</v>
+        <v>3.559252336962658</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.289400766575227</v>
+        <v>4.288213980130571</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.00445597141556</v>
+        <v>1.004302581411238</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.868785161246635</v>
+        <v>2.868290668868632</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.330495608151075</v>
+        <v>2.379041527916847</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.8937655915433851</v>
+        <v>0.9177230004929982</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.85529800684369</v>
+        <v>4.90330968583401</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.966264045137812</v>
+        <v>5.015511607531529</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.639385934857877</v>
+        <v>6.712643044637574</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.789467138527812</v>
+        <v>5.888814463822385</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.318870026510538</v>
+        <v>7.418778062529213</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.197178814704074</v>
+        <v>6.320875435732319</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.777027961390665</v>
+        <v>5.925717509168493</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.846694247455282</v>
+        <v>5.018693007021945</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>181</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.530133693222552</v>
+        <v>5.500937898869921</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.36646141231342</v>
+        <v>3.365274625868764</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.419203839713077</v>
+        <v>2.419050449708756</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.311859922528015</v>
+        <v>5.311365430150012</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.878542745122843</v>
+        <v>5.927088664888615</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.070944399067358</v>
+        <v>5.094901808016971</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.538720227646458</v>
+        <v>5.586731906636778</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.75673445678796</v>
+        <v>1.805982019181677</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.010669427337007</v>
+        <v>5.083926537116703</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.055778255316596</v>
+        <v>3.15512558061117</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.956049472746919</v>
+        <v>4.055957508765594</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.990427625102143</v>
+        <v>4.114124246130388</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.402098918818893</v>
+        <v>-1.253409371041066</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.176363268592397</v>
+        <v>-1.004364509025734</v>
       </c>
     </row>
     <row r="32">
@@ -1924,49 +1924,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.337265787647439</v>
+        <v>4.567513745889272</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.635170603674545</v>
+        <v>3.897578669865844</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.967671946192233</v>
+        <v>6.2435667089484</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.8251698170533</v>
+        <v>4.090345727332057</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.468698445775864</v>
+        <v>6.7974436183436</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.675163384501801</v>
+        <v>7.983471146294946</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.77227120705382</v>
+        <v>11.11916208903291</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.6688389269034</v>
+        <v>12.02319234234819</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>12.97149313401701</v>
+        <v>13.35608274691005</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>14.39430161041442</v>
+        <v>14.35873818435988</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.00778227033607</v>
+        <v>11.41487170942656</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>14.67852405905503</v>
+        <v>14.66938547875495</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>13.34928229665071</v>
+        <v>13.36098554305868</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>11.75683612869546</v>
+        <v>11.78354638680923</v>
       </c>
     </row>
     <row r="33">
@@ -1976,101 +1976,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.770096115214649</v>
+        <v>1.52214623962913</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>6.636642815673056</v>
+        <v>6.390582057699092</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.027296532132617</v>
+        <v>4.787166650029569</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.347805076530712</v>
+        <v>4.110599078340989</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.619232122625249</v>
+        <v>4.427801550292322</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.131181051045786</v>
+        <v>5.910264488466062</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.45132899137473</v>
+        <v>6.252834205692224</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>12.05713484151517</v>
+        <v>11.83538854208309</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.99615268499237</v>
+        <v>11.79841593294625</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>11.14623388866252</v>
+        <v>11.37781315858291</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.7512493295926</v>
+        <v>11.57689851749844</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.1904857815431</v>
+        <v>12.44151686776656</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.9849098270151</v>
+        <v>13.25603636055759</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.78149567967078</v>
+        <v>11.08572638386325</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 93.98</t>
+          <t>X ≈ 93.97</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>198</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.084740535122222</v>
+        <v>4.055544740769591</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.061799093295129</v>
+        <v>-1.062985879739784</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.4464694679491998</v>
+        <v>-0.4466228579535212</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.21910921099272</v>
+        <v>3.218614718614717</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.6606176376950046</v>
+        <v>0.7091635574607764</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.388432823215446</v>
+        <v>2.436444502205767</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.9213641794287</v>
+        <v>1.970611741822417</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.3452305077544224</v>
+        <v>0.4184876175341188</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.545816761929601</v>
+        <v>4.645164087224174</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.846166108719913</v>
+        <v>4.946074144738589</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.395695776226752</v>
+        <v>6.519392397254997</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.99574694311535</v>
+        <v>8.144436490893177</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.221482593341896</v>
+        <v>8.393481352908559</v>
       </c>
     </row>
   </sheetData>
@@ -2210,53 +2210,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 8.15</t>
+          <t>X &gt; 8.151</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4080</v>
+        <v>4091</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1210873899396248</v>
+        <v>0.1214671224814339</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2578490005464857</v>
+        <v>0.257186351960577</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2674652841180603</v>
+        <v>0.2667517462060829</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1176792635970045</v>
+        <v>0.1173755530010041</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1307407321761289</v>
+        <v>0.1292177580027882</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1724948201894065</v>
+        <v>0.1714532913999207</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.199056802178049</v>
+        <v>0.1973626145147946</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1370007210564239</v>
+        <v>0.1354428697973091</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1629919656627479</v>
+        <v>0.1607836244785474</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1836347063097321</v>
+        <v>0.180739622799706</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2621184313584877</v>
+        <v>0.2589982070520023</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2368510823502135</v>
+        <v>0.2332226124289605</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1980938624434145</v>
+        <v>0.1939640242916951</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2661944174654778</v>
+        <v>0.261316388673194</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3974</v>
+        <v>3985</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.08563135533996302</v>
+        <v>-0.08389871833370677</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.02787733684454707</v>
+        <v>-0.02773974817142744</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.08285845189148944</v>
+        <v>-0.08262249395313859</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.164881296491771</v>
+        <v>-0.1644019309851572</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1623243100272589</v>
+        <v>-0.1643689635429482</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.05319576051802244</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1482375732891796</v>
+        <v>-0.1502946326295671</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.09909163499697371</v>
+        <v>-0.1013481477270517</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.07994889037426844</v>
+        <v>0.07596464343218656</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1489064826663764</v>
+        <v>0.143390269832409</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2349292747020826</v>
+        <v>0.2291455812704015</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2080649407085886</v>
+        <v>0.2011307742529667</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2297854413048057</v>
+        <v>0.2215042076999865</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2685257475818261</v>
+        <v>0.258936405314671</v>
       </c>
     </row>
     <row r="8">
@@ -2318,101 +2318,101 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3846</v>
+        <v>3857</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2134892360280105</v>
+        <v>-0.2103702228197974</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.05512441865168682</v>
+        <v>0.05506983898791873</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.01448564213595915</v>
+        <v>-0.01443124168743282</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2332043813623699</v>
+        <v>-0.2324984299383104</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2386473860836418</v>
+        <v>-0.2421498873860344</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1606152634200697</v>
+        <v>-0.1622222619407978</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.283104769163053</v>
+        <v>-0.2864364815447971</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1389586752866805</v>
+        <v>-0.1428082463063447</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.02208211916847347</v>
+        <v>0.01570264716757208</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.04365225976508924</v>
+        <v>0.03495947701955515</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.269219715717405</v>
+        <v>0.2598334999487193</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1883520688830345</v>
+        <v>0.1771411729099697</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2507639706824278</v>
+        <v>0.2372149755845783</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1792821174440675</v>
+        <v>0.1639210362339014</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 17.18</t>
+          <t>X &gt; 17.19</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3697</v>
+        <v>3708</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3515359766259962</v>
+        <v>-0.3595741904783836</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1422504115464136</v>
+        <v>-0.1540579339740091</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.06400403694006229</v>
+        <v>-0.07605325661466367</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3507136466639693</v>
+        <v>-0.36198547215497</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3617484953025354</v>
+        <v>-0.3792229991712048</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2115989759447601</v>
+        <v>-0.2140801068323626</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3626198198458397</v>
+        <v>-0.3677753545040048</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1939013573869346</v>
+        <v>-0.1997183768114184</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.077964161793588</v>
+        <v>-0.08724299861935236</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.03270400780090199</v>
+        <v>0.01970692943942964</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2215414840952832</v>
+        <v>0.2079083313908825</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.13601871362998</v>
+        <v>0.1195448653319886</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2719431944332982</v>
+        <v>0.2518138503600582</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1343904110373728</v>
+        <v>0.1386024669617143</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3551</v>
+        <v>3561</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2777164795941403</v>
+        <v>-0.282597114884183</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.006718763543872797</v>
+        <v>-0.001360658921754521</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2605325928800397</v>
+        <v>-0.2958298139729081</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4802438703828358</v>
+        <v>-0.5433458857463407</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4976353047669875</v>
+        <v>-0.5558704052736942</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1006555127336171</v>
+        <v>-0.1428717625063598</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1700448406881563</v>
+        <v>-0.2035278517318204</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.08747562468669656</v>
+        <v>-0.1085081163215591</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.04858102529763642</v>
+        <v>-0.06135285108931043</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.0107221784022542</v>
+        <v>-0.02821769695705711</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1943851411494606</v>
+        <v>0.1761527081504823</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.21650522203619</v>
+        <v>0.1939998243182117</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.3473110209537325</v>
+        <v>0.3199819511101865</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.2069526131684327</v>
+        <v>0.2199175769858925</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3408</v>
+        <v>3418</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1417347439846424</v>
+        <v>-0.1305497810913607</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1582033227792223</v>
+        <v>-0.1505319006970396</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1275990788622892</v>
+        <v>-0.1779413009283886</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.03999633081694753</v>
+        <v>-0.09063204475244646</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2403711731298728</v>
+        <v>-0.2876544177324192</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.01484060857686131</v>
+        <v>-0.0733142525078776</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.02498075012783119</v>
+        <v>-0.0755249881389517</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.05136030239287948</v>
+        <v>0.01387311062440943</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.09448151726333265</v>
+        <v>0.06456853187918909</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1989176920753835</v>
+        <v>0.1758656085744335</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4505975196029297</v>
+        <v>0.4266029050101139</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3549420968693724</v>
+        <v>0.325878309004068</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.3915358177774735</v>
+        <v>0.3567024674177119</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.2945015149523584</v>
+        <v>0.3005567883631599</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3278</v>
+        <v>3287</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.03336358298190589</v>
+        <v>-0.03516496791765178</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1049781683726181</v>
+        <v>0.09869164888790749</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.02992188072924762</v>
+        <v>-0.06587831130194388</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.03528500505700549</v>
+        <v>-0.1018237082066946</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2830657717418319</v>
+        <v>-0.3175166181555653</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.09183927864420127</v>
+        <v>0.01605917421959191</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.08470717194181532</v>
+        <v>0.01619335855035331</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.06089476868505983</v>
+        <v>0.006287649838746745</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.07769689672795721</v>
+        <v>0.03010531425817931</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2507317656250905</v>
+        <v>0.2093162471210164</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6121516734245986</v>
+        <v>0.5826833983691131</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.51134895228261</v>
+        <v>0.4756776578880846</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.365755756077192</v>
+        <v>0.3410375378592008</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4084529682317282</v>
+        <v>0.4248384283788056</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3165</v>
+        <v>3174</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1009479493145093</v>
+        <v>0.08504388445557254</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1756144118348928</v>
+        <v>0.1546657784404886</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.04998849542749895</v>
+        <v>-0.001663347838182005</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.0713377682323042</v>
+        <v>0.00231575160752584</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1660602381631975</v>
+        <v>-0.2036472703642147</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2747161496174826</v>
+        <v>0.1950431902236716</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2704071405209802</v>
+        <v>0.1973395718826936</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3255703305581719</v>
+        <v>0.2666028140174461</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2505335380574394</v>
+        <v>0.1981539694384082</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3653955622472722</v>
+        <v>0.3186124518906652</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6838863305209983</v>
+        <v>0.6495680068726699</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.609875488036792</v>
+        <v>0.5681927432845555</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5688715541546543</v>
+        <v>0.5373419231687038</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4154602849499156</v>
+        <v>0.4262857675655241</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3045</v>
+        <v>3053</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1213752951612292</v>
+        <v>0.1059771221372117</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1646103845878102</v>
+        <v>0.1428903506702781</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.04964794595402111</v>
+        <v>-0.004042605163824931</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.09714639884087717</v>
+        <v>-0.1686611817501884</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1260096976048999</v>
+        <v>-0.1670726263670304</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1237475871843756</v>
+        <v>0.04026786627388645</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2537703572968226</v>
+        <v>0.1759468555824526</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3952765312938098</v>
+        <v>0.3318418438902171</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2868853230554294</v>
+        <v>0.2294242085754021</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2759347507475169</v>
+        <v>0.2236584549855536</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4838234705152047</v>
+        <v>0.4449106776065292</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4196794553828411</v>
+        <v>0.3906747791756686</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.3279358270283765</v>
+        <v>0.308711857526113</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2252642522959647</v>
+        <v>0.2488182131586214</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2922</v>
+        <v>2930</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3840225779240356</v>
+        <v>0.3869570231021058</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3944212472650008</v>
+        <v>0.3901751199605812</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1206350240699905</v>
+        <v>0.08323231037370249</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2012212152965986</v>
+        <v>0.1449035275774619</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1597068908826174</v>
+        <v>0.1331441547019452</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5100548340157403</v>
+        <v>0.440036085526323</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.8201180970059738</v>
+        <v>0.7545505283608946</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.9532212112857295</v>
+        <v>0.8685267720703251</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9798254309950281</v>
+        <v>0.8997669869444422</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8675700457081987</v>
+        <v>0.7921730582440603</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8534670441522678</v>
+        <v>0.7926710827407035</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.6825063874726851</v>
+        <v>0.6461993480728623</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7414794219073855</v>
+        <v>0.7139390911020342</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.6592068585815625</v>
+        <v>0.6753443514950987</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2785</v>
+        <v>2792</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5971083073325048</v>
+        <v>0.6014761579456334</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4370779694916891</v>
+        <v>0.432650267059131</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2409201879218514</v>
+        <v>0.2015915697884836</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3190950963601935</v>
+        <v>0.2598936496574282</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2663524047200951</v>
+        <v>0.2359272574528291</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.7269251759552517</v>
+        <v>0.6518766989632354</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.092474676468193</v>
+        <v>1.020712377812217</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.255393384286755</v>
+        <v>1.163326288867673</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.250550759808327</v>
+        <v>1.162144660403747</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.354477879387836</v>
+        <v>1.268881577083391</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.257496649314369</v>
+        <v>1.207905052238779</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.112341588025167</v>
+        <v>1.087116886239322</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.15897709018752</v>
+        <v>1.142082120117763</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.025646313125002</v>
+        <v>1.053606964323563</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2673</v>
+        <v>2680</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7081925110546052</v>
+        <v>0.7138911568498756</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4397889618177047</v>
+        <v>0.4555552361167443</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2146190289602146</v>
+        <v>0.1940622474835578</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2159533522937451</v>
+        <v>0.1747482282730246</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1461375115643904</v>
+        <v>0.1330932685967525</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.6508485137170084</v>
+        <v>0.5923763629471992</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.8857377106548583</v>
+        <v>0.8301163945721655</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.8880402862917123</v>
+        <v>0.8118778154644701</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.9976031496558448</v>
+        <v>0.924103266752887</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.103991097881703</v>
+        <v>1.03276256359549</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.011523385188291</v>
+        <v>0.9405206613783079</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7840234978878016</v>
+        <v>0.7375907929990788</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9250398724082913</v>
+        <v>0.9019255930298087</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9263086315012714</v>
+        <v>0.9485092437573428</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2553</v>
+        <v>2560</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7404818609143007</v>
+        <v>0.7477890724988967</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2226186885845536</v>
+        <v>0.2392637831655975</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.07281100835321297</v>
+        <v>-0.09421159183664685</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.038555359684743</v>
+        <v>-0.08146929212919218</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1255868623484346</v>
+        <v>-0.1411987142212965</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.07588155565407817</v>
+        <v>0.01444506309041316</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.521168632007587</v>
+        <v>0.4614031870629276</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.584512294631601</v>
+        <v>0.5031846398775386</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.8194321957384005</v>
+        <v>0.7395427609242731</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.049039352108707</v>
+        <v>0.9699898536742992</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.8051685894615233</v>
+        <v>0.7268021589691358</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7612075330428496</v>
+        <v>0.7068744019958828</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.9677703499213806</v>
+        <v>0.9364724301372505</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.075997186986918</v>
+        <v>1.090766706443915</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2431</v>
+        <v>2437</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.232666242752479</v>
+        <v>1.222455853537951</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.9345700142762539</v>
+        <v>0.9333832278315981</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4577305129844831</v>
+        <v>0.4575771229801617</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.610510912739251</v>
+        <v>0.587461164194842</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4644049979505311</v>
+        <v>0.4675185476581944</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7023539425058374</v>
+        <v>0.6582359499403978</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.010286377251482</v>
+        <v>0.9668863851302021</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.306249213984778</v>
+        <v>1.239666673577389</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.556437601314435</v>
+        <v>1.489932472319126</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.858308192068094</v>
+        <v>1.815057523018304</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.777013039566839</v>
+        <v>1.734019250287304</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.729120521416199</v>
+        <v>1.710117871115465</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.72032302063262</v>
+        <v>1.725300527235277</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.8226526651002</v>
+        <v>1.851243214445553</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2314</v>
+        <v>2319</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.249140028111619</v>
+        <v>1.239888175113016</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.104103137290124</v>
+        <v>1.102916350845469</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6230876818149582</v>
+        <v>0.6229342918106369</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6239467193231079</v>
+        <v>0.6234522269451048</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.2819386999133897</v>
+        <v>0.3066912274334612</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.689445175218637</v>
+        <v>0.6657208169725308</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.18991918946864</v>
+        <v>1.165651187427962</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.481326655157915</v>
+        <v>1.432893028165793</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.049830526961166</v>
+        <v>1.999628914069966</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.323507236249291</v>
+        <v>2.296973252616773</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.162021289743628</v>
+        <v>2.13595484044076</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.153184230344422</v>
+        <v>2.150999542445575</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.992324647558227</v>
+        <v>2.014573828042167</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.001984239012074</v>
+        <v>2.048008513257194</v>
       </c>
     </row>
     <row r="21">
@@ -2994,101 +2994,101 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2189</v>
+        <v>2193</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.189854603300574</v>
+        <v>1.181775139561516</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.220255377541804</v>
+        <v>1.219068591097148</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6886850871780155</v>
+        <v>0.6885316971736941</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9557091363751269</v>
+        <v>0.9552146439971239</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3718199480765279</v>
+        <v>0.4203658678422997</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6487864767380387</v>
+        <v>0.6475517514583018</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.456475181992623</v>
+        <v>1.453288731088286</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.882620579041266</v>
+        <v>1.853849039560394</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.304521914281992</v>
+        <v>2.272872782452787</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.733726005115223</v>
+        <v>2.725833987319511</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.757439648134152</v>
+        <v>2.749691715798022</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.928866681256949</v>
+        <v>2.944657358771664</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.691447668966838</v>
+        <v>2.731897973019514</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.643085557658431</v>
+        <v>2.707345023817361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 56.34</t>
+          <t>X &gt; 56.33</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2099</v>
+        <v>2103</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.229835634546525</v>
+        <v>1.244641026824048</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.474025374023128</v>
+        <v>1.493967390480222</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.079253989268089</v>
+        <v>1.100229402165517</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.257052872152364</v>
+        <v>1.230113443380198</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.7663370583525762</v>
+        <v>0.7884154198795414</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.9209898700999375</v>
+        <v>0.966098703795943</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.862228370309417</v>
+        <v>1.904016081046954</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.136371394435912</v>
+        <v>2.151450082432504</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.43617328473816</v>
+        <v>2.447335295454536</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.920223044863754</v>
+        <v>2.954938003274833</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.810805354921804</v>
+        <v>2.845899790641262</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.035750443913621</v>
+        <v>3.094270997811201</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.949091729714077</v>
+        <v>3.031970893406189</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.888976974985866</v>
+        <v>2.995709050713998</v>
       </c>
     </row>
     <row r="23">
@@ -3098,49 +3098,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.473743919087809</v>
+        <v>1.444548124735178</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.676159841137341</v>
+        <v>1.674973054692686</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.281388456382302</v>
+        <v>1.281235066377981</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.411613599970664</v>
+        <v>1.411119107592661</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.07483538188756</v>
+        <v>1.123381301653332</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.120320242756897</v>
+        <v>1.14427765170651</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.071758010572879</v>
+        <v>2.091178237544021</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.490596594349462</v>
+        <v>2.481768650964213</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.458696142915301</v>
+        <v>2.444796041827416</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.22330812357837</v>
+        <v>3.233058141113183</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.018606965318178</v>
+        <v>3.028917693577093</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.153893291235569</v>
+        <v>3.187840098448291</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.44009965285656</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.211748522053831</v>
+        <v>3.293616202665575</v>
       </c>
     </row>
     <row r="24">
@@ -3150,49 +3150,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.807842626897717</v>
+        <v>1.778646832545085</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.114610716039536</v>
+        <v>2.11342392959488</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.133797775610553</v>
+        <v>1.133644385606232</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.583681949566518</v>
+        <v>1.583187457188515</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.045392396470824</v>
+        <v>1.093938316236596</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.236213415983379</v>
+        <v>1.260170824932992</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.874228950802603</v>
+        <v>1.892109301504021</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.610657108721625</v>
+        <v>2.598359652468567</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.389674952198845</v>
+        <v>2.401557528147968</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.979756155868998</v>
+        <v>3.016194583987215</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.881721664275467</v>
+        <v>2.918607146573663</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.502766483297464</v>
+        <v>3.562815439612507</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.882615629984045</v>
+        <v>3.966805088967696</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.468351280210577</v>
+        <v>3.57653189024785</v>
       </c>
     </row>
     <row r="25">
@@ -3202,49 +3202,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.61101222058673</v>
+        <v>1.581816426234099</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.905655723935453</v>
+        <v>1.904468937490797</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.174561469225253</v>
+        <v>1.174408079220932</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.809270917746353</v>
+        <v>1.80877642536835</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.327035176309856</v>
+        <v>1.375581096075628</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.568355394285746</v>
+        <v>1.592312803235359</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.156290774929893</v>
+        <v>2.204302453920214</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.011060922518595</v>
+        <v>3.027707361698305</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.00616401557518</v>
+        <v>3.046788564220698</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.670546957888064</v>
+        <v>3.736412898203923</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.578016298786586</v>
+        <v>3.64438007398622</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.173246946935514</v>
+        <v>4.263084927943041</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.482204338153792</v>
+        <v>4.596626552948727</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.922746494269276</v>
+        <v>4.060918051735385</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1675</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.907143670958192</v>
+        <v>1.87794787660556</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.907897876401826</v>
+        <v>1.90671108995717</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.572827984184094</v>
+        <v>1.572674594179773</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.120963575533651</v>
+        <v>2.120469083155648</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.940882977661843</v>
+        <v>1.989428897427615</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.760645066998407</v>
+        <v>1.78460247594802</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.571457095791956</v>
+        <v>2.619468774782277</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.417821287826108</v>
+        <v>3.467068850219825</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.476242116377954</v>
+        <v>3.54949922615765</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.118860633480935</v>
+        <v>4.218207958775508</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.093263952832679</v>
+        <v>4.193171988851354</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.72465703056114</v>
+        <v>4.848353651589385</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.961222595158176</v>
+        <v>5.109912142936004</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.35113734986232</v>
+        <v>4.523136109428982</v>
       </c>
     </row>
     <row r="27">
@@ -3309,150 +3309,150 @@
         <v>1539</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.294912429504635</v>
+        <v>2.265716635152003</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.048248753594798</v>
+        <v>2.047061967150142</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.718454626799478</v>
+        <v>1.718301236795156</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.563429607944691</v>
+        <v>2.562935115566688</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.674912634446137</v>
+        <v>2.723458554211909</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.517445858363232</v>
+        <v>2.541403267312845</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.472371626452485</v>
+        <v>3.520383305442806</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.434802657779457</v>
+        <v>4.484050220173174</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.50377501717611</v>
+        <v>4.577032126955807</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.823446864121102</v>
+        <v>4.922794189415676</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.61874570586091</v>
+        <v>4.718653741879585</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.432850953732803</v>
+        <v>5.556547574761048</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.272609132258253</v>
+        <v>5.421298680036081</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.108481234726504</v>
+        <v>5.280479994293167</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 74.41</t>
+          <t>X &gt; 74.4</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1401</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.194315946624812</v>
+        <v>2.165120152272181</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.724457476687327</v>
+        <v>2.723270690242671</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.757951616557563</v>
+        <v>2.757798226553241</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.030931935021009</v>
+        <v>3.030437442643006</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.99228549398812</v>
+        <v>3.040831413753892</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.004149173873039</v>
+        <v>3.028106582822652</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.346990563357757</v>
+        <v>4.395002242348077</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.236096080884366</v>
+        <v>5.285343643278082</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.674757036424403</v>
+        <v>5.748014146204099</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.181012401407891</v>
+        <v>6.280359726702464</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.33319918033542</v>
+        <v>6.433107216354095</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.152730794503739</v>
+        <v>7.276427415531984</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.589824766315246</v>
+        <v>6.738514314093074</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.45867247935405</v>
+        <v>6.630671238920712</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 77.42</t>
+          <t>X &gt; 77.41</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1250</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.799083969465642</v>
+        <v>2.76988817511301</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.347897876401824</v>
+        <v>3.346711089957168</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.113126491646774</v>
+        <v>3.112973101642453</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.963351635235149</v>
+        <v>3.962857142857146</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.745062082139448</v>
+        <v>3.79360800190522</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.882436111774531</v>
+        <v>3.906393520724144</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.637725752508359</v>
+        <v>5.68573743149868</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6.930657108721626</v>
+        <v>6.979904671115342</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.589674952198848</v>
+        <v>7.662932061978545</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.859756155868993</v>
+        <v>7.959103481163567</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.655054997608801</v>
+        <v>7.754963033627476</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.569433149964119</v>
+        <v>8.693129770992364</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.669282296650707</v>
+        <v>7.817971844428534</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.335017946877237</v>
+        <v>7.507016706443899</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>1103</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.00412476728976</v>
+        <v>2.974928972937128</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.296837132974801</v>
+        <v>3.295650346530145</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.99272757958876</v>
+        <v>2.992574189584438</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.029571036867054</v>
+        <v>4.029076544489051</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.944590640616333</v>
+        <v>3.993136560382105</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.24196467025142</v>
+        <v>4.265922079201033</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.789167275627129</v>
+        <v>5.83717895461745</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.772687933744294</v>
+        <v>6.821935496138011</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.527662259542467</v>
+        <v>7.600919369322163</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.675023608271523</v>
+        <v>7.774370933566097</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.379660618642347</v>
+        <v>7.479568654661023</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.320657084687603</v>
+        <v>8.444353705715848</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.628520737267223</v>
+        <v>7.777210285045051</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.038299905172806</v>
+        <v>7.210298664739469</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>930</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.895428055487152</v>
+        <v>2.86623226113452</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.112198951670635</v>
+        <v>3.111012165225979</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.36258885723818</v>
+        <v>3.362435467233858</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.245502172869557</v>
+        <v>4.245007680491554</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.244847028376007</v>
+        <v>4.293392948141779</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.864801703172382</v>
+        <v>4.888759112121996</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.962887042830943</v>
+        <v>6.010898721821263</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.108721624850659</v>
+        <v>7.157969187244376</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.692900758650467</v>
+        <v>7.766157868430163</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.025777661245343</v>
+        <v>8.125124986539916</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.390968976103423</v>
+        <v>7.490877012122098</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.715669709103899</v>
+        <v>8.839366330132144</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.972938210629209</v>
+        <v>8.121627758407037</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.445985688812726</v>
+        <v>7.617984448379389</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>749</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.258736839959639</v>
+        <v>2.229541045607007</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.590563073756257</v>
+        <v>3.590409683751936</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.987810914273858</v>
+        <v>3.987316421895855</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.850055406572032</v>
+        <v>3.898601326337804</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.814986178530212</v>
+        <v>4.838943587479825</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.06538930391023</v>
+        <v>6.113400982900551</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.4020589778805</v>
+        <v>8.451306540274217</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.341076821357724</v>
+        <v>8.414333931137421</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>9.226805555067912</v>
+        <v>9.326152880362486</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.221036306020011</v>
+        <v>8.320944342038686</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9.85755063995078</v>
+        <v>9.981247260979025</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.23846787742508</v>
+        <v>10.38715742520291</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.529624088399281</v>
+        <v>9.701622847965943</v>
       </c>
     </row>
     <row r="33">
@@ -3618,153 +3618,153 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.394320264361681</v>
+        <v>1.263473080773394</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.807708840484992</v>
+        <v>2.699163920145843</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.601973372554156</v>
+        <v>2.494105177114157</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.055449933911895</v>
+        <v>3.944743935309965</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.761016713519403</v>
+        <v>2.700777813225976</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3.625498493627084</v>
+        <v>3.539601067893955</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.107895884833503</v>
+        <v>4.044982714517552</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.043473743882316</v>
+        <v>6.975376369228549</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.415383836886939</v>
+        <v>6.372366024242694</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.077752375150659</v>
+        <v>7.246650650974885</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.062087133714662</v>
+        <v>7.042510203438795</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.852608953366776</v>
+        <v>8.044073167218777</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.944745434646933</v>
+        <v>9.158349202919105</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>8.603373334400878</v>
+        <v>8.841356329085421</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 92.48</t>
+          <t>X &gt; 92.47</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>282</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.065183260245796</v>
+        <v>1.035987465893164</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.5460028328180329</v>
+        <v>-0.5471896192626886</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4776654987389719</v>
+        <v>0.4775121087346506</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.799380004029466</v>
+        <v>3.798885511651463</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.133430876465688</v>
+        <v>1.18197679623146</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.430804906100775</v>
+        <v>1.454762315050388</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.055314404990639</v>
+        <v>2.10332608398096</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.652075548437942</v>
+        <v>2.701323110831659</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.527263604681124</v>
+        <v>1.600520714460821</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.514224240975373</v>
+        <v>3.613571566269947</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.954913153637172</v>
+        <v>3.054821189655847</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.05312109322653</v>
+        <v>4.176817714254774</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>5.406019885303188</v>
+        <v>5.554709433081015</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.695585322763776</v>
+        <v>6.867584082330438</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 95.49</t>
+          <t>X &gt; 95.48</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.6698026383065852</v>
+        <v>0.6686158518619294</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.167161159044667</v>
+        <v>5.166666666666664</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>4.92624563558406</v>
+        <v>4.950203044533673</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1.270106704889322</v>
+        <v>1.318118383879643</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.374466632531153</v>
+        <v>4.42371419492487</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.313484476008377</v>
+        <v>4.386741585788073</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-1.503040240486435</v>
+        <v>-1.403132204467759</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1.468662088131111</v>
+        <v>-1.344965467102867</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.6983367509683305</v>
+        <v>-0.5496472031905029</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>3.098827470686771</v>
+        <v>3.270826230253434</v>
       </c>
     </row>
   </sheetData>
@@ -3904,53 +3904,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 8.15</t>
+          <t>X &lt; 8.151</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.861868411486739</v>
+        <v>-4.891064205839371</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.473054504550568</v>
+        <v>-6.474241290995224</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.43925446073418</v>
+        <v>-10.4394078507385</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.975695983812471</v>
+        <v>-1.976190476190474</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.513985536908166</v>
+        <v>-2.465439617142394</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.407087697749276</v>
+        <v>-3.383130288799663</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.491798057015444</v>
+        <v>-3.443786378025123</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.577914319849803</v>
+        <v>-1.528666757456087</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.63889647637258</v>
+        <v>-1.565639366592883</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.488815272702439</v>
+        <v>-2.389467947407866</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-5.040090659559688</v>
+        <v>-4.916394038531443</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.079289131920717</v>
+        <v>-2.93059958414289</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.615458243598944</v>
+        <v>-7.443459484032282</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>190</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.255926074728812</v>
+        <v>2.226730280376181</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.276318929033401</v>
+        <v>3.275132142588745</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.881547544278362</v>
+        <v>2.881394154274041</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.117035845761457</v>
+        <v>5.116541353383454</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.105062082139447</v>
+        <v>5.153608001905219</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.297172953879802</v>
+        <v>3.321130362829415</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.844041541982051</v>
+        <v>5.892053220972372</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.324341319247942</v>
+        <v>4.373588881641659</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.105464425883056</v>
+        <v>1.178721535662753</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2707701599204881</v>
+        <v>-0.1714228346259148</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.054418686601728</v>
+        <v>-1.954510650583053</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.493724744772713</v>
+        <v>-1.370028123744468</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.913875598086122</v>
+        <v>-1.765186050308294</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.267087316280652</v>
+        <v>-3.095088556713989</v>
       </c>
     </row>
     <row r="8">
@@ -4015,98 +4015,98 @@
         <v>318</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.864995919151184</v>
+        <v>2.835800124798553</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.9393444172823209</v>
+        <v>0.9381576308376651</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.8590384413323164</v>
+        <v>0.8588850513279951</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.81945226416596</v>
+        <v>3.818957771787957</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.910093528680328</v>
+        <v>3.9586394484461</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.264071331900318</v>
+        <v>3.288028740849931</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.066153425464336</v>
+        <v>5.114165104454656</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.026757737652446</v>
+        <v>3.076005300046162</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.393448537104511</v>
+        <v>1.466705646884208</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.172460558384714</v>
+        <v>1.271807883679287</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.547963870315733</v>
+        <v>-1.448055834297058</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.5701894915453138</v>
+        <v>-0.4464928705170692</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.30480575366375</v>
+        <v>-1.156116205885922</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.7646046946321903</v>
+        <v>-0.5926059350655279</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 17.18</t>
+          <t>X &lt; 17.19</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>467</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.979469408437808</v>
+        <v>3.045443730668573</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2.224814364624521</v>
+        <v>2.316967500213572</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.9735119306189404</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.459197459646283</v>
+        <v>3.548840048840049</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.563306193488479</v>
+        <v>3.700616548913771</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.575883649247764</v>
+        <v>2.599841058197377</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.990102626170035</v>
+        <v>4.038114305160356</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.452370170820132</v>
+        <v>2.501617733213848</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.748989727359451</v>
+        <v>1.822246837139147</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.8990709310295912</v>
+        <v>0.9984182563241646</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5904268011064033</v>
+        <v>-0.4905187650877281</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.08634963818682451</v>
+        <v>0.2100462592150691</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.9761995020644889</v>
+        <v>-0.8275099542866613</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1080655649000519</v>
+        <v>-0.1501995676460268</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.753611656762068</v>
+        <v>1.770986721155019</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.7938913617438388</v>
+        <v>0.8340131901187107</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.864918022591411</v>
+        <v>2.055784087102879</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.298074762270979</v>
+        <v>3.639626125086544</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.411251007220883</v>
+        <v>3.729659781840496</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.265628294184964</v>
+        <v>1.50418930678574</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.832383732964395</v>
+        <v>2.021581587342844</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.202448639666258</v>
+        <v>1.32266889875762</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.141466483143482</v>
+        <v>1.214723592923178</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.9430134848592218</v>
+        <v>1.042360810153795</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2388863704693733</v>
+        <v>-0.1389783344506981</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3673746676254481</v>
+        <v>-0.2436780465972035</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.11325841996166</v>
+        <v>-0.9645688721838326</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.4706590514914311</v>
+        <v>-0.5526575606570674</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.7555436788447736</v>
+        <v>0.7008973494249489</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.390064322901154</v>
+        <v>1.345767446444711</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.8631925418449313</v>
+        <v>1.083091057081518</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5971164965297291</v>
+        <v>0.8197903014416781</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.511931302747108</v>
+        <v>1.715287791931459</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.6204017656714953</v>
+        <v>0.8797443748634421</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.7998921990077008</v>
+        <v>1.023632168340797</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.332823555220962</v>
+        <v>0.4993776618926873</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2718413986981858</v>
+        <v>0.4038291596038803</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1817762087281025</v>
+        <v>-0.08242888343352917</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.311180141096614</v>
+        <v>-1.211272105077938</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.8805007998377263</v>
+        <v>-0.7568041788094817</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.036450860548754</v>
+        <v>-0.8877613127709267</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.7371513652920711</v>
+        <v>-0.7708168470567571</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2217866721683421</v>
+        <v>0.227318342710781</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1871771556810984</v>
+        <v>0.2083870676107935</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.3554688339891214</v>
+        <v>0.4850401407486018</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.4856939775774833</v>
+        <v>0.7266560255387091</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.411368388445759</v>
+        <v>1.529446928079714</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1321658415042606</v>
+        <v>0.4095962082941327</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2726807074633228</v>
+        <v>0.5226881041444287</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2560625141270307</v>
+        <v>0.4554602266709011</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3076929702168769</v>
+        <v>0.4809095900684355</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.3170006008877664</v>
+        <v>-0.1678706470704014</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.647827885274083</v>
+        <v>-1.547919849255408</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.275611895080921</v>
+        <v>-1.151915274052676</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.7318901948938148</v>
+        <v>-0.6461722997156087</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.007374829646459</v>
+        <v>-1.072803113375912</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2331637827821069</v>
+        <v>-0.1810731727561645</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.04614807764413342</v>
+        <v>0.01969424159244682</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.05858103710131957</v>
+        <v>0.2206044197792352</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.08890608078958451</v>
+        <v>0.3055555555555429</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.8493178263951933</v>
+        <v>0.9629426593034296</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.451709742371321</v>
+        <v>-0.1998490240074631</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3366199018372882</v>
+        <v>-0.106899384421709</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.6038883458238331</v>
+        <v>-0.4188204284862564</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2652701027462001</v>
+        <v>-0.1021726239636251</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.6156883995755678</v>
+        <v>-0.4718745627486101</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.61959035703655</v>
+        <v>-1.519682321017875</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.385412004881033</v>
+        <v>-1.261715383852788</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.250717703349281</v>
+        <v>-1.157372810916115</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>-0.9083279489007481</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2527520376644716</v>
+        <v>-0.209226869134767</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.007719623282390842</v>
+        <v>0.06600312535539388</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.05858103710131957</v>
+        <v>0.2032385883681229</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5453124195488712</v>
+        <v>0.7358598000759216</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.6309087844567429</v>
+        <v>0.7387143848839415</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.03701721694388027</v>
+        <v>0.2622409031553801</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2259462617518864</v>
+        <v>-0.01614533937165419</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6930149055386252</v>
+        <v>-0.5223175511068732</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.3083642634874195</v>
+        <v>-0.1548615323275087</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2670174626693296</v>
+        <v>-0.1283052454615472</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.8282248597887119</v>
+        <v>-0.7283168237700366</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.6551877242553203</v>
+        <v>-0.5810235266903376</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4007177033492866</v>
+        <v>-0.3522955352505974</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.214079461523113</v>
+        <v>-0.2815037926648287</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.8343296851528237</v>
+        <v>-0.83547067656162</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5178049348431628</v>
+        <v>-0.5047721636313511</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.1093634681925835</v>
+        <v>-0.02131716948991169</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2201021800259042</v>
+        <v>-0.08739026336791511</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1158214519970997</v>
+        <v>-0.05405972972418027</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.8626241291893137</v>
+        <v>-0.6967079980608233</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.509583484439425</v>
+        <v>-1.354262568501305</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.8963308430856</v>
+        <v>-1.697373151142465</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.876991714467813</v>
+        <v>-1.691555117508635</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.602412518829802</v>
+        <v>-1.430022421001631</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.566149821668311</v>
+        <v>-1.429884478411047</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.166258168363854</v>
+        <v>-1.086789907722498</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.30075792861075</v>
+        <v>-1.240983978864627</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.191487689193607</v>
+        <v>-1.232902972270956</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.143244302407098</v>
+        <v>-1.145169296151352</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.5129264186090268</v>
+        <v>-0.5013348870543268</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3292451641738978</v>
+        <v>-0.2485211512311025</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4159397602818444</v>
+        <v>-0.29531683270001</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3034700942886062</v>
+        <v>-0.242075451332191</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.163001343033855</v>
+        <v>-1.009891576468071</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.826164341490184</v>
+        <v>-1.680372078587766</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.220926405378151</v>
+        <v>-2.035928061400881</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.137295402103391</v>
+        <v>-1.962464763418275</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.336454979344317</v>
+        <v>-2.170282800424886</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.14048769414228</v>
+        <v>-2.046539856545934</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.849683432222704</v>
+        <v>-1.804628725030767</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.940572775813052</v>
+        <v>-1.910560331999513</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.747679660084323</v>
+        <v>-1.806128629781689</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.210862554598528</v>
+        <v>-1.214430761764064</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.4466171737654037</v>
+        <v>-0.4720264515710753</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2393818695572349</v>
+        <v>-0.2013126126432567</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1760463580759009</v>
+        <v>-0.1018237082066946</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.04543959010135978</v>
+        <v>-0.02270603668426219</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.8851893062856604</v>
+        <v>-0.7786663993823808</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.237458193979933</v>
+        <v>-1.136594347315437</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.303189045124526</v>
+        <v>-1.166761995551326</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.43106083375433</v>
+        <v>-1.301177344292299</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.612083309013954</v>
+        <v>-1.488266345271683</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.445667893957463</v>
+        <v>-1.322017594295041</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.039676026191273</v>
+        <v>-0.9598114054782201</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.288787408443113</v>
+        <v>-1.251192035170121</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.361266426026845</v>
+        <v>-1.403484965796899</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.119529891920493</v>
+        <v>-1.125496440271597</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.03637456941861217</v>
+        <v>-0.06251967927361335</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2499685969099446</v>
+        <v>0.2822038708732322</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2563547312103722</v>
+        <v>0.3226600985221637</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3991797291982735</v>
+        <v>0.4216301830512421</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1392782170376989</v>
+        <v>0.2352714492075023</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.5027076840241378</v>
+        <v>-0.4084760169899013</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.6601788045910695</v>
+        <v>-0.5321940943167505</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.9688389796896928</v>
+        <v>-0.844294621159186</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.323401738867844</v>
+        <v>-1.201934837748674</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.9365682985498154</v>
+        <v>-0.81562447410289</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.8678886107302404</v>
+        <v>-0.7850880507898097</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.191660631388991</v>
+        <v>-1.145991003868673</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.428085715444297</v>
+        <v>-1.454221683648974</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1733</v>
+        <v>1738</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.676318329384927</v>
+        <v>-1.65296896774413</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.015621387542971</v>
+        <v>-1.007574624328555</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.516792955994184</v>
+        <v>-0.513327641639421</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6742548089535774</v>
+        <v>-0.6386073880353109</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4645581710251108</v>
+        <v>-0.4674566804073237</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.7425581344855416</v>
+        <v>-0.6789902135255659</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.114955490299458</v>
+        <v>-1.052600677383829</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.582024134086197</v>
+        <v>-1.48771000778374</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.873155887847183</v>
+        <v>-1.780785666076532</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.289374529220247</v>
+        <v>-2.229553235254343</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.17508325123913</v>
+        <v>-2.115640068038239</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.109529386058938</v>
+        <v>-2.083881723260504</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.09477768028124</v>
+        <v>-2.102948224576636</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.299188631310869</v>
+        <v>-2.340440140506608</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1850</v>
+        <v>1856</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.512132392213573</v>
+        <v>-1.492981203901977</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.103410685795275</v>
+        <v>-1.095430237665965</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6614424738704585</v>
+        <v>-0.6573536257276587</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6100176370020591</v>
+        <v>-0.6058030929413576</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.177956785785085</v>
+        <v>-0.2083222930009399</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.6352997372820681</v>
+        <v>-0.6036493977307913</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.205185298704571</v>
+        <v>-1.172104758517413</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.618345586696165</v>
+        <v>-1.555519603857803</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.272319656965578</v>
+        <v>-2.208534891272393</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.608248159125615</v>
+        <v>-2.573799744642891</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.406337339142418</v>
+        <v>-2.372675481703347</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.396873545500242</v>
+        <v>-2.393199615444665</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.193667460237464</v>
+        <v>-2.220929609529456</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.262819890960593</v>
+        <v>-2.319793638383686</v>
       </c>
     </row>
     <row r="21">
@@ -4688,101 +4688,101 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1975</v>
+        <v>1982</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.271238611179513</v>
+        <v>-1.256350541035431</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.091597837163491</v>
+        <v>-1.084261828799107</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6523629129950024</v>
+        <v>-0.6485923775346691</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.8987987938410811</v>
+        <v>-0.8932874354561164</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.248473271395909</v>
+        <v>-0.3009374526402411</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5066547973163793</v>
+        <v>-0.503254720481884</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.348940914158298</v>
+        <v>-1.341150451859782</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.866514608450082</v>
+        <v>-1.83047762264723</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.281032118508222</v>
+        <v>-2.243258174558946</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.75049144392888</v>
+        <v>-2.738338613499067</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.77657290936795</v>
+        <v>-2.764533188034996</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.968047881902343</v>
+        <v>-2.981870229007633</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.703349282296656</v>
+        <v>-2.745094217094397</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.70346306578098</v>
+        <v>-2.771651305665067</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 56.34</t>
+          <t>X &lt; 56.33</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2065</v>
+        <v>2072</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.203807596799415</v>
+        <v>-1.214526412219037</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.247357668439072</v>
+        <v>-1.262194860138813</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9895266680251922</v>
+        <v>-1.006470009255281</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.123057631174127</v>
+        <v>-1.091052559352271</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6216399941521971</v>
+        <v>-0.6416827237074614</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.7328295887085616</v>
+        <v>-0.7755295561989328</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.638795986622064</v>
+        <v>-1.676109610348355</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.960937094176927</v>
+        <v>-1.972087629173387</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.215155965675542</v>
+        <v>-2.224212858579953</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.701133162642364</v>
+        <v>-2.733536210551271</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.589896646491781</v>
+        <v>-2.622868291673726</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.819826646842849</v>
+        <v>-2.876397712132025</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.730098148654228</v>
+        <v>-2.811724248190849</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.720381568861256</v>
+        <v>-2.826342366915171</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2182</v>
+        <v>2190</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.29478464367304</v>
+        <v>-1.261814049126649</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.285164652123967</v>
+        <v>-1.27766674837163</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.062215974106643</v>
+        <v>-1.056767925163541</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.135999666729226</v>
+        <v>-1.129870129870142</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.8272962359592739</v>
+        <v>-0.867310597458129</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.8252730788976166</v>
+        <v>-0.8429422390574715</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.641579231487974</v>
+        <v>-1.652924380062537</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.062923138191948</v>
+        <v>-2.049093507391028</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.986731083466445</v>
+        <v>-1.970780922076116</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.67506543607977</v>
+        <v>-2.679219217104432</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.489201295297377</v>
+        <v>-2.494266332537599</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.613350732819761</v>
+        <v>-2.639716944336101</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.871514771603977</v>
+        <v>-2.919189269218194</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.712791402343655</v>
+        <v>-2.78266365885289</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2289</v>
+        <v>2298</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.437437769664783</v>
+        <v>-1.406693391308444</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.504020348913535</v>
+        <v>-1.495886312640238</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.831521027935473</v>
+        <v>-0.827434000999375</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.156822504947705</v>
+        <v>-1.150903689031949</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7137532488710079</v>
+        <v>-0.7501631294341777</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.8285007073975734</v>
+        <v>-0.8442049181310125</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.305367929408852</v>
+        <v>-1.315390551147736</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.946728512193403</v>
+        <v>-1.931692551106877</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.722966721733144</v>
+        <v>-1.728470456475648</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.200671231832708</v>
+        <v>-2.225014676959802</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.120093344450538</v>
+        <v>-2.145045658245621</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.629519272558802</v>
+        <v>-2.672087620311977</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.938927310336183</v>
+        <v>-3.000505754527524</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.646039283354298</v>
+        <v>-2.728179116010402</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2381</v>
+        <v>2391</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.164576707508857</v>
+        <v>-1.137399678464355</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.207486738982794</v>
+        <v>-1.20107084928545</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7854933326945002</v>
+        <v>-0.7817812697147488</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.218573050957325</v>
+        <v>-1.212619741774269</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8555909107446098</v>
+        <v>-0.8880586647614521</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9962238547246329</v>
+        <v>-1.009621485528456</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.393627410457697</v>
+        <v>-1.423253394189381</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.070164005647875</v>
+        <v>-2.075481227925124</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.025077772025789</v>
+        <v>-2.048587136685896</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.517266904927652</v>
+        <v>-2.557973763095312</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.44783090843147</v>
+        <v>-2.489180658937272</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.894435922633441</v>
+        <v>-2.951834708740186</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.124269340628885</v>
+        <v>-3.199352570287182</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.750055551652785</v>
+        <v>-2.844367651565292</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2489</v>
+        <v>2500</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.241907237568732</v>
+        <v>-1.216836854731795</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.07330964059139</v>
+        <v>-1.067811203036463</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9668735083532169</v>
+        <v>-0.962534664187892</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.29542387496894</v>
+        <v>-1.28941377347752</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.171959535154386</v>
+        <v>-1.199520734643201</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.01326272683179</v>
+        <v>-1.024962141157829</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.517210144927525</v>
+        <v>-1.542918332362497</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.123290787069955</v>
+        <v>-2.147182320105721</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.122915264320795</v>
+        <v>-2.163016041813869</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.550416327083269</v>
+        <v>-2.606263930977008</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.53300278730292</v>
+        <v>-2.589327817351347</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.958788447787782</v>
+        <v>-3.029332259383331</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.116581157164546</v>
+        <v>-3.20334762778257</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.748806882371447</v>
+        <v>-2.852983293556086</v>
       </c>
     </row>
     <row r="27">
@@ -5000,153 +5000,153 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2625</v>
+        <v>2636</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.305783354264456</v>
+        <v>-1.283233757691811</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.001468828186731</v>
+        <v>-0.9966121728827133</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.9208644036491265</v>
+        <v>-0.9169475632612105</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.377521230040003</v>
+        <v>-1.371504157218453</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.44011635369958</v>
+        <v>-1.46264908694166</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.312337910253568</v>
+        <v>-1.320958975493703</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.832730174543308</v>
+        <v>-1.853331808001883</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.431745019746636</v>
+        <v>-2.450587380360815</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.434659648561606</v>
+        <v>-2.467624545367151</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.617870318075475</v>
+        <v>-2.665441973381888</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.497821714719962</v>
+        <v>-2.546241968267182</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.97590373621783</v>
+        <v>-3.036362268431439</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.880725319495518</v>
+        <v>-2.956332289056483</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.824982053122753</v>
+        <v>-2.914591791279918</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 74.41</t>
+          <t>X &lt; 74.4</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2763</v>
+        <v>2774</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.076016895087662</v>
+        <v>-1.056936367405825</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.191201222697273</v>
+        <v>-1.18589479661857</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.314559160840602</v>
+        <v>-1.309289016849462</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.417593189864029</v>
+        <v>-1.411740558292287</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.395659418582049</v>
+        <v>-1.414843309629099</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.367682978806485</v>
+        <v>-1.374469167989005</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.010794103087299</v>
+        <v>-2.02728666055453</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.4949550256229</v>
+        <v>-2.510167271330694</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.681423313697096</v>
+        <v>-2.708136667780359</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.934114462128846</v>
+        <v>-2.973135539714768</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.011148906946516</v>
+        <v>-3.050164802166556</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.427673540813458</v>
+        <v>-3.477187231889481</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.141311046330479</v>
+        <v>-3.204730858274161</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.113364246390937</v>
+        <v>-3.188816026072317</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 77.42</t>
+          <t>X &lt; 77.41</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2914</v>
+        <v>2925</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.165576092030761</v>
+        <v>-1.148641436867926</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.255465076434824</v>
+        <v>-1.250251797342806</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.256104277583994</v>
+        <v>-1.251332075469264</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.586470526187568</v>
+        <v>-1.580311511316623</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.490900969519807</v>
+        <v>-1.506242032177944</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.517481752701855</v>
+        <v>-1.522123356193688</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.234482395386195</v>
+        <v>-2.246813728119321</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.820575767990704</v>
+        <v>-2.83124510711734</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.069180820325982</v>
+        <v>-3.089286368055582</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.181559813973365</v>
+        <v>-3.212518232731966</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.093878838524212</v>
+        <v>-3.125419480033727</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.487082625070165</v>
+        <v>-3.527437362591513</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.10011736029611</v>
+        <v>-3.152745858920746</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.993273062045198</v>
+        <v>-3.0564020969749</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3061</v>
+        <v>3072</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.049556238732144</v>
+        <v>-1.035233380802701</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.016931280773576</v>
+        <v>-1.012873864647247</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.003800591686556</v>
+        <v>-1.000163453660825</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.344600171993768</v>
+        <v>-1.33962176694169</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.311876028609738</v>
+        <v>-1.324808096764045</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.388049388388382</v>
+        <v>-1.391788297457666</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.911739697296063</v>
+        <v>-1.922343114133007</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.296392125057309</v>
+        <v>-2.306073236616946</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.535830592484771</v>
+        <v>-2.553382530156654</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.585529325370814</v>
+        <v>-2.612391967471027</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.479044219101382</v>
+        <v>-2.506500381006667</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.818878962344073</v>
+        <v>-2.853779793093516</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.568418552467513</v>
+        <v>-2.613320052740356</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.390352846980974</v>
+        <v>-2.444389543556092</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3234</v>
+        <v>3245</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.8024435944394952</v>
+        <v>-0.7912659071460411</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.7341230724583099</v>
+        <v>-0.7312993490971849</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.8967348334687841</v>
+        <v>-0.8936608049914483</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.119903605208762</v>
+        <v>-1.115975422427042</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.11757128202953</v>
+        <v>-1.127891690780707</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.266286898712821</v>
+        <v>-1.268964610231897</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.550524787448438</v>
+        <v>-1.559231818193808</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.908602150537625</v>
+        <v>-1.916459524516767</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.04576808577584</v>
+        <v>-2.060144861098372</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.138069662537433</v>
+        <v>-2.159726928193166</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.955399126580261</v>
+        <v>-1.977844848145921</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.336870929145896</v>
+        <v>-2.364954614594332</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.12212419484851</v>
+        <v>-2.15822039217035</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.003213345639757</v>
+        <v>-2.046511798949005</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3415</v>
+        <v>3426</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.468080557955588</v>
+        <v>-0.4600972857767829</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.5175471192211702</v>
+        <v>-0.5156274789782671</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.7215495153584683</v>
+        <v>-0.7192061244267904</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.7800060289984359</v>
+        <v>-0.7773989689007266</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.747741656178313</v>
+        <v>-0.7561445454019164</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9311893629552301</v>
+        <v>-0.933536589933972</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.175553031828279</v>
+        <v>-1.182471132439559</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.714674665613366</v>
+        <v>-1.720141948931271</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.672313351894722</v>
+        <v>-1.683264382206822</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.863110179316742</v>
+        <v>-1.879263865775208</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.642358694608873</v>
+        <v>-1.659350177221171</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.001711128642846</v>
+        <v>-2.022856226673909</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.083972972670125</v>
+        <v>-2.110432007336847</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.9593890809412</v>
+        <v>-1.991453813112422</v>
       </c>
     </row>
     <row r="33">
@@ -5312,153 +5312,153 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3635</v>
+        <v>3645</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1782844515869826</v>
+        <v>-0.1591003432030007</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2670404290547168</v>
+        <v>-0.2513419589900607</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3179212318858546</v>
+        <v>-0.3021253666288715</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5020530286880458</v>
+        <v>-0.4857338284150927</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3120619573775585</v>
+        <v>-0.303425386162651</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.411453539611685</v>
+        <v>-0.3989555074718609</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4538283386503394</v>
+        <v>-0.4447773549197152</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.9060031494492051</v>
+        <v>-0.8957677474001358</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7872481247242291</v>
+        <v>-0.7809035544598046</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.8802493401463991</v>
+        <v>-0.9047167435555323</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.8773694114071375</v>
+        <v>-0.874466790933937</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.9927334708772264</v>
+        <v>-1.020497868163105</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.150167648343782</v>
+        <v>-1.18112853955391</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.129246152159894</v>
+        <v>-1.163820056244703</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 92.48</t>
+          <t>X &lt; 92.47</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3882</v>
+        <v>3893</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.05472861076542301</v>
+        <v>-0.05235452842000399</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1708665461501511</v>
+        <v>0.170475494566638</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.02121793783224035</v>
+        <v>0.02116982295393655</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1942639865531461</v>
+        <v>-0.1936788550931539</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.0009757290168650457</v>
+        <v>-0.002722085229578397</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.00397852822697331</v>
+        <v>0.00214332846574905</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.01526473347774981</v>
+        <v>-0.01887795311670004</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.08247046329483254</v>
+        <v>-0.08598914781259026</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.0250750036524181</v>
+        <v>0.0194225699313435</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1158279923553991</v>
+        <v>-0.1230725516822133</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.0744688119150112</v>
+        <v>-0.08187474871339617</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1543567573479265</v>
+        <v>-0.1633528990974895</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2510267427518045</v>
+        <v>-0.261658355879625</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3714014245807675</v>
+        <v>-0.3834739177533635</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 95.49</t>
+          <t>X &lt; 95.48</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4080</v>
+        <v>4091</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1455193469393805</v>
+        <v>0.1458335942163274</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1112214345640865</v>
+        <v>0.1109518893722239</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.001417629594968162</v>
+        <v>-0.001410126051354155</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.02902000290666251</v>
+        <v>-0.02893022607726436</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.03291730346495569</v>
+        <v>0.03165678239302849</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.001261943477082639</v>
+        <v>0.0006799320439867529</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.101185502936552</v>
+        <v>0.09975402495891217</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.01463165595608729</v>
+        <v>0.01340235234551557</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.04059294485490739</v>
+        <v>0.03871331197854744</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1101773115986688</v>
+        <v>0.107479549539633</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.164151250364128</v>
+        <v>0.1612942500417347</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1633576967549075</v>
+        <v>0.1599267414296932</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1490862662660035</v>
+        <v>0.1450881689642287</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.04560618217136181</v>
+        <v>0.0413212774534415</v>
       </c>
     </row>
   </sheetData>
